--- a/A股每日选股报告页面设计/public/reports/20260625/stock_pick_20260625.xlsx
+++ b/A股每日选股报告页面设计/public/reports/20260625/stock_pick_20260625.xlsx
@@ -14,9 +14,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="准确性评估" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'选股详情'!$A$1:$AP$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'选股详情'!$A$1:$AU$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'技术诊断'!$A$3:$F$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'筛选漏斗'!$A$3:$E$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'筛选漏斗'!$A$3:$E$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -366,12 +366,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'选股详情'!$V$2:$V$21</f>
+              <f>'选股详情'!$AA$2:$AA$21</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'选股详情'!$S$2:$S$21</f>
+              <f>'选股详情'!$X$2:$X$21</f>
             </numRef>
           </yVal>
         </ser>
@@ -490,9 +490,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="StockPicks" displayName="StockPicks" ref="A1:AP21" headerRowCount="1">
-  <autoFilter ref="A1:AP21"/>
-  <tableColumns count="42">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="StockPicks" displayName="StockPicks" ref="A1:AU21" headerRowCount="1">
+  <autoFilter ref="A1:AU21"/>
+  <tableColumns count="47">
     <tableColumn id="1" name="排名"/>
     <tableColumn id="2" name="代码"/>
     <tableColumn id="3" name="名称"/>
@@ -511,30 +511,35 @@
     <tableColumn id="16" name="资金"/>
     <tableColumn id="17" name="板块"/>
     <tableColumn id="18" name="领涨"/>
-    <tableColumn id="19" name="ADX"/>
-    <tableColumn id="20" name="+DI"/>
-    <tableColumn id="21" name="-DI"/>
-    <tableColumn id="22" name="量比"/>
-    <tableColumn id="23" name="主力净流入比"/>
-    <tableColumn id="24" name="板块排名分位"/>
-    <tableColumn id="25" name="板块内排名分位"/>
-    <tableColumn id="26" name="入场时机"/>
-    <tableColumn id="27" name="计划持有日"/>
-    <tableColumn id="28" name="止损价"/>
-    <tableColumn id="29" name="第一止盈"/>
-    <tableColumn id="30" name="第二止盈"/>
-    <tableColumn id="31" name="移动止盈"/>
-    <tableColumn id="32" name="盈亏比"/>
-    <tableColumn id="33" name="退出计划"/>
-    <tableColumn id="34" name="第1日止损"/>
-    <tableColumn id="35" name="第1日止盈"/>
-    <tableColumn id="36" name="第1日计划"/>
-    <tableColumn id="37" name="第2日止损"/>
-    <tableColumn id="38" name="第2日止盈"/>
-    <tableColumn id="39" name="第2日计划"/>
-    <tableColumn id="40" name="第3日止损"/>
-    <tableColumn id="41" name="第3日止盈"/>
-    <tableColumn id="42" name="第3日计划"/>
+    <tableColumn id="19" name="事件上下文"/>
+    <tableColumn id="20" name="近期大事件"/>
+    <tableColumn id="21" name="融资融券"/>
+    <tableColumn id="22" name="龙虎榜"/>
+    <tableColumn id="23" name="上下文说明"/>
+    <tableColumn id="24" name="ADX"/>
+    <tableColumn id="25" name="+DI"/>
+    <tableColumn id="26" name="-DI"/>
+    <tableColumn id="27" name="量比"/>
+    <tableColumn id="28" name="主力净流入比"/>
+    <tableColumn id="29" name="板块排名分位"/>
+    <tableColumn id="30" name="板块内排名分位"/>
+    <tableColumn id="31" name="入场时机"/>
+    <tableColumn id="32" name="计划持有日"/>
+    <tableColumn id="33" name="止损价"/>
+    <tableColumn id="34" name="第一止盈"/>
+    <tableColumn id="35" name="第二止盈"/>
+    <tableColumn id="36" name="移动止盈"/>
+    <tableColumn id="37" name="盈亏比"/>
+    <tableColumn id="38" name="退出计划"/>
+    <tableColumn id="39" name="第1日止损"/>
+    <tableColumn id="40" name="第1日止盈"/>
+    <tableColumn id="41" name="第1日计划"/>
+    <tableColumn id="42" name="第2日止损"/>
+    <tableColumn id="43" name="第2日止盈"/>
+    <tableColumn id="44" name="第2日计划"/>
+    <tableColumn id="45" name="第3日止损"/>
+    <tableColumn id="46" name="第3日止盈"/>
+    <tableColumn id="47" name="第3日计划"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1074,7 +1079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP21"/>
+  <dimension ref="A1:AU21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1096,29 +1101,34 @@
     <col width="8" customWidth="1" min="17" max="17"/>
     <col width="8" customWidth="1" min="18" max="18"/>
     <col width="8" customWidth="1" min="19" max="19"/>
-    <col width="8" customWidth="1" min="20" max="20"/>
+    <col width="9" customWidth="1" min="20" max="20"/>
     <col width="8" customWidth="1" min="21" max="21"/>
-    <col width="8" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="9" customWidth="1" min="22" max="22"/>
+    <col width="23" customWidth="1" min="23" max="23"/>
     <col width="8" customWidth="1" min="24" max="24"/>
-    <col width="9" customWidth="1" min="25" max="25"/>
-    <col width="14" customWidth="1" min="26" max="26"/>
+    <col width="8" customWidth="1" min="25" max="25"/>
+    <col width="8" customWidth="1" min="26" max="26"/>
     <col width="8" customWidth="1" min="27" max="27"/>
-    <col width="8" customWidth="1" min="28" max="28"/>
+    <col width="10" customWidth="1" min="28" max="28"/>
     <col width="8" customWidth="1" min="29" max="29"/>
-    <col width="8" customWidth="1" min="30" max="30"/>
-    <col width="8" customWidth="1" min="31" max="31"/>
+    <col width="9" customWidth="1" min="30" max="30"/>
+    <col width="14" customWidth="1" min="31" max="31"/>
     <col width="8" customWidth="1" min="32" max="32"/>
-    <col width="28" customWidth="1" min="33" max="33"/>
+    <col width="8" customWidth="1" min="33" max="33"/>
     <col width="8" customWidth="1" min="34" max="34"/>
     <col width="8" customWidth="1" min="35" max="35"/>
-    <col width="28" customWidth="1" min="36" max="36"/>
+    <col width="8" customWidth="1" min="36" max="36"/>
     <col width="8" customWidth="1" min="37" max="37"/>
-    <col width="8" customWidth="1" min="38" max="38"/>
-    <col width="28" customWidth="1" min="39" max="39"/>
+    <col width="28" customWidth="1" min="38" max="38"/>
+    <col width="8" customWidth="1" min="39" max="39"/>
     <col width="8" customWidth="1" min="40" max="40"/>
-    <col width="8" customWidth="1" min="41" max="41"/>
-    <col width="28" customWidth="1" min="42" max="42"/>
+    <col width="28" customWidth="1" min="41" max="41"/>
+    <col width="8" customWidth="1" min="42" max="42"/>
+    <col width="8" customWidth="1" min="43" max="43"/>
+    <col width="28" customWidth="1" min="44" max="44"/>
+    <col width="8" customWidth="1" min="45" max="45"/>
+    <col width="8" customWidth="1" min="46" max="46"/>
+    <col width="28" customWidth="1" min="47" max="47"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -1214,120 +1224,145 @@
       </c>
       <c r="S1" s="7" t="inlineStr">
         <is>
+          <t>事件上下文</t>
+        </is>
+      </c>
+      <c r="T1" s="7" t="inlineStr">
+        <is>
+          <t>近期大事件</t>
+        </is>
+      </c>
+      <c r="U1" s="7" t="inlineStr">
+        <is>
+          <t>融资融券</t>
+        </is>
+      </c>
+      <c r="V1" s="7" t="inlineStr">
+        <is>
+          <t>龙虎榜</t>
+        </is>
+      </c>
+      <c r="W1" s="7" t="inlineStr">
+        <is>
+          <t>上下文说明</t>
+        </is>
+      </c>
+      <c r="X1" s="7" t="inlineStr">
+        <is>
           <t>ADX</t>
         </is>
       </c>
-      <c r="T1" s="7" t="inlineStr">
+      <c r="Y1" s="7" t="inlineStr">
         <is>
           <t>+DI</t>
         </is>
       </c>
-      <c r="U1" s="7" t="inlineStr">
+      <c r="Z1" s="7" t="inlineStr">
         <is>
           <t>-DI</t>
         </is>
       </c>
-      <c r="V1" s="7" t="inlineStr">
+      <c r="AA1" s="7" t="inlineStr">
         <is>
           <t>量比</t>
         </is>
       </c>
-      <c r="W1" s="7" t="inlineStr">
+      <c r="AB1" s="7" t="inlineStr">
         <is>
           <t>主力净流入比</t>
         </is>
       </c>
-      <c r="X1" s="7" t="inlineStr">
+      <c r="AC1" s="7" t="inlineStr">
         <is>
           <t>板块排名分位</t>
         </is>
       </c>
-      <c r="Y1" s="7" t="inlineStr">
+      <c r="AD1" s="7" t="inlineStr">
         <is>
           <t>板块内排名分位</t>
         </is>
       </c>
-      <c r="Z1" s="7" t="inlineStr">
+      <c r="AE1" s="7" t="inlineStr">
         <is>
           <t>入场时机</t>
         </is>
       </c>
-      <c r="AA1" s="7" t="inlineStr">
+      <c r="AF1" s="7" t="inlineStr">
         <is>
           <t>计划持有日</t>
         </is>
       </c>
-      <c r="AB1" s="7" t="inlineStr">
+      <c r="AG1" s="7" t="inlineStr">
         <is>
           <t>止损价</t>
         </is>
       </c>
-      <c r="AC1" s="7" t="inlineStr">
+      <c r="AH1" s="7" t="inlineStr">
         <is>
           <t>第一止盈</t>
         </is>
       </c>
-      <c r="AD1" s="7" t="inlineStr">
+      <c r="AI1" s="7" t="inlineStr">
         <is>
           <t>第二止盈</t>
         </is>
       </c>
-      <c r="AE1" s="7" t="inlineStr">
+      <c r="AJ1" s="7" t="inlineStr">
         <is>
           <t>移动止盈</t>
         </is>
       </c>
-      <c r="AF1" s="7" t="inlineStr">
+      <c r="AK1" s="7" t="inlineStr">
         <is>
           <t>盈亏比</t>
         </is>
       </c>
-      <c r="AG1" s="7" t="inlineStr">
+      <c r="AL1" s="7" t="inlineStr">
         <is>
           <t>退出计划</t>
         </is>
       </c>
-      <c r="AH1" s="7" t="inlineStr">
+      <c r="AM1" s="7" t="inlineStr">
         <is>
           <t>第1日止损</t>
         </is>
       </c>
-      <c r="AI1" s="7" t="inlineStr">
+      <c r="AN1" s="7" t="inlineStr">
         <is>
           <t>第1日止盈</t>
         </is>
       </c>
-      <c r="AJ1" s="7" t="inlineStr">
+      <c r="AO1" s="7" t="inlineStr">
         <is>
           <t>第1日计划</t>
         </is>
       </c>
-      <c r="AK1" s="7" t="inlineStr">
+      <c r="AP1" s="7" t="inlineStr">
         <is>
           <t>第2日止损</t>
         </is>
       </c>
-      <c r="AL1" s="7" t="inlineStr">
+      <c r="AQ1" s="7" t="inlineStr">
         <is>
           <t>第2日止盈</t>
         </is>
       </c>
-      <c r="AM1" s="7" t="inlineStr">
+      <c r="AR1" s="7" t="inlineStr">
         <is>
           <t>第2日计划</t>
         </is>
       </c>
-      <c r="AN1" s="7" t="inlineStr">
+      <c r="AS1" s="7" t="inlineStr">
         <is>
           <t>第3日止损</t>
         </is>
       </c>
-      <c r="AO1" s="7" t="inlineStr">
+      <c r="AT1" s="7" t="inlineStr">
         <is>
           <t>第3日止盈</t>
         </is>
       </c>
-      <c r="AP1" s="7" t="inlineStr">
+      <c r="AU1" s="7" t="inlineStr">
         <is>
           <t>第3日计划</t>
         </is>
@@ -1391,83 +1426,106 @@
         <v>9.75</v>
       </c>
       <c r="S2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" s="4" t="inlineStr">
+        <is>
+          <t>近期无重大公告</t>
+        </is>
+      </c>
+      <c r="U2" s="4" t="inlineStr">
+        <is>
+          <t>无两融数据</t>
+        </is>
+      </c>
+      <c r="V2" s="4" t="inlineStr">
+        <is>
+          <t>近期未上龙虎榜</t>
+        </is>
+      </c>
+      <c r="W2" s="4" t="inlineStr">
+        <is>
+          <t>近期无重大公告；无两融数据；近期未上龙虎榜</t>
+        </is>
+      </c>
+      <c r="X2" s="4" t="n">
         <v>61.1</v>
       </c>
-      <c r="T2" s="4" t="n">
+      <c r="Y2" s="4" t="n">
         <v>34.61</v>
       </c>
-      <c r="U2" s="4" t="n">
+      <c r="Z2" s="4" t="n">
         <v>5.92</v>
       </c>
-      <c r="V2" s="4" t="n">
+      <c r="AA2" s="4" t="n">
         <v>1.55</v>
       </c>
-      <c r="W2" s="4" t="n">
+      <c r="AB2" s="4" t="n">
         <v>0.185032</v>
       </c>
-      <c r="X2" s="4" t="n">
+      <c r="AC2" s="4" t="n">
         <v>0.025</v>
       </c>
-      <c r="Y2" s="4" t="n">
+      <c r="AD2" s="4" t="n">
         <v>0.025</v>
       </c>
-      <c r="Z2" s="4" t="inlineStr">
+      <c r="AE2" s="4" t="inlineStr">
         <is>
           <t>🟠 远离均线，不宜追高</t>
         </is>
       </c>
-      <c r="AA2" s="4" t="n">
+      <c r="AF2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="AB2" s="4" t="n">
+      <c r="AG2" s="4" t="n">
         <v>6.3</v>
       </c>
-      <c r="AC2" s="4" t="n">
+      <c r="AH2" s="4" t="n">
         <v>7.53</v>
       </c>
-      <c r="AD2" s="4" t="n">
+      <c r="AI2" s="4" t="n">
         <v>8.06</v>
       </c>
-      <c r="AE2" s="4" t="n">
+      <c r="AJ2" s="4" t="n">
         <v>6.3</v>
       </c>
-      <c r="AF2" s="4" t="n">
+      <c r="AK2" s="4" t="n">
         <v>1.6</v>
       </c>
-      <c r="AG2" s="4" t="inlineStr">
+      <c r="AL2" s="4" t="inlineStr">
         <is>
           <t>1日短线计划；T+1看7.20/止损6.53；T+2看7.34/止损6.30；T+3看7.53/止损6.30</t>
         </is>
       </c>
-      <c r="AH2" s="4" t="n">
+      <c r="AM2" s="4" t="n">
         <v>6.53</v>
       </c>
-      <c r="AI2" s="4" t="n">
+      <c r="AN2" s="4" t="n">
         <v>7.2</v>
       </c>
-      <c r="AJ2" s="4" t="inlineStr">
+      <c r="AO2" s="4" t="inlineStr">
         <is>
           <t>T+1：冲到7.20先减仓，跌破6.53止损；若高开低走不恋战</t>
         </is>
       </c>
-      <c r="AK2" s="4" t="n">
+      <c r="AP2" s="4" t="n">
         <v>6.3</v>
       </c>
-      <c r="AL2" s="4" t="n">
+      <c r="AQ2" s="4" t="n">
         <v>7.34</v>
       </c>
-      <c r="AM2" s="4" t="inlineStr">
+      <c r="AR2" s="4" t="inlineStr">
         <is>
           <t>T+2：未突破7.34且量能转弱则减仓，跌破6.30退出</t>
         </is>
       </c>
-      <c r="AN2" s="4" t="n">
+      <c r="AS2" s="4" t="n">
         <v>6.3</v>
       </c>
-      <c r="AO2" s="4" t="n">
+      <c r="AT2" s="4" t="n">
         <v>7.53</v>
       </c>
-      <c r="AP2" s="4" t="inlineStr">
+      <c r="AU2" s="4" t="inlineStr">
         <is>
           <t>T+3：到7.53分批止盈，跌破6.30或MA5失守退出</t>
         </is>
@@ -1531,83 +1589,106 @@
         <v>7.75</v>
       </c>
       <c r="S3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>近期无重大公告</t>
+        </is>
+      </c>
+      <c r="U3" s="4" t="inlineStr">
+        <is>
+          <t>无两融数据</t>
+        </is>
+      </c>
+      <c r="V3" s="4" t="inlineStr">
+        <is>
+          <t>近期未上龙虎榜</t>
+        </is>
+      </c>
+      <c r="W3" s="4" t="inlineStr">
+        <is>
+          <t>近期无重大公告；无两融数据；近期未上龙虎榜</t>
+        </is>
+      </c>
+      <c r="X3" s="4" t="n">
         <v>54.7</v>
       </c>
-      <c r="T3" s="4" t="n">
+      <c r="Y3" s="4" t="n">
         <v>45.73</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="Z3" s="4" t="n">
         <v>11.01</v>
       </c>
-      <c r="V3" s="4" t="n">
+      <c r="AA3" s="4" t="n">
         <v>1.86</v>
       </c>
-      <c r="W3" s="4" t="n">
+      <c r="AB3" s="4" t="n">
         <v>0.111074</v>
       </c>
-      <c r="X3" s="4" t="n">
+      <c r="AC3" s="4" t="n">
         <v>0.225</v>
       </c>
-      <c r="Y3" s="4" t="n">
+      <c r="AD3" s="4" t="n">
         <v>0.225</v>
       </c>
-      <c r="Z3" s="4" t="inlineStr">
+      <c r="AE3" s="4" t="inlineStr">
         <is>
           <t>🟡 首日上涨，可关注</t>
         </is>
       </c>
-      <c r="AA3" s="4" t="n">
+      <c r="AF3" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="AB3" s="4" t="n">
+      <c r="AG3" s="4" t="n">
         <v>27.49</v>
       </c>
-      <c r="AC3" s="4" t="n">
+      <c r="AH3" s="4" t="n">
         <v>32.87</v>
       </c>
-      <c r="AD3" s="4" t="n">
+      <c r="AI3" s="4" t="n">
         <v>34.94</v>
       </c>
-      <c r="AE3" s="4" t="n">
+      <c r="AJ3" s="4" t="n">
         <v>27.87</v>
       </c>
-      <c r="AF3" s="4" t="n">
+      <c r="AK3" s="4" t="n">
         <v>1.6</v>
       </c>
-      <c r="AG3" s="4" t="inlineStr">
+      <c r="AL3" s="4" t="inlineStr">
         <is>
           <t>1日短线计划；T+1看31.42/止损28.53；T+2看32.04/止损27.73；T+3看32.87/止损27.87</t>
         </is>
       </c>
-      <c r="AH3" s="4" t="n">
+      <c r="AM3" s="4" t="n">
         <v>28.53</v>
       </c>
-      <c r="AI3" s="4" t="n">
+      <c r="AN3" s="4" t="n">
         <v>31.42</v>
       </c>
-      <c r="AJ3" s="4" t="inlineStr">
+      <c r="AO3" s="4" t="inlineStr">
         <is>
           <t>T+1：冲到31.42先减仓，跌破28.53止损；若高开低走不恋战</t>
         </is>
       </c>
-      <c r="AK3" s="4" t="n">
+      <c r="AP3" s="4" t="n">
         <v>27.73</v>
       </c>
-      <c r="AL3" s="4" t="n">
+      <c r="AQ3" s="4" t="n">
         <v>32.04</v>
       </c>
-      <c r="AM3" s="4" t="inlineStr">
+      <c r="AR3" s="4" t="inlineStr">
         <is>
           <t>T+2：未突破32.04且量能转弱则减仓，跌破27.73退出</t>
         </is>
       </c>
-      <c r="AN3" s="4" t="n">
+      <c r="AS3" s="4" t="n">
         <v>27.87</v>
       </c>
-      <c r="AO3" s="4" t="n">
+      <c r="AT3" s="4" t="n">
         <v>32.87</v>
       </c>
-      <c r="AP3" s="4" t="inlineStr">
+      <c r="AU3" s="4" t="inlineStr">
         <is>
           <t>T+3：到32.87分批止盈，跌破27.87或MA5失守退出</t>
         </is>
@@ -1671,83 +1752,106 @@
         <v>7.88</v>
       </c>
       <c r="S4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>近期无重大公告</t>
+        </is>
+      </c>
+      <c r="U4" s="4" t="inlineStr">
+        <is>
+          <t>无两融数据</t>
+        </is>
+      </c>
+      <c r="V4" s="4" t="inlineStr">
+        <is>
+          <t>近期未上龙虎榜</t>
+        </is>
+      </c>
+      <c r="W4" s="4" t="inlineStr">
+        <is>
+          <t>近期无重大公告；无两融数据；近期未上龙虎榜</t>
+        </is>
+      </c>
+      <c r="X4" s="4" t="n">
         <v>51.1</v>
       </c>
-      <c r="T4" s="4" t="n">
+      <c r="Y4" s="4" t="n">
         <v>28.38</v>
       </c>
-      <c r="U4" s="4" t="n">
+      <c r="Z4" s="4" t="n">
         <v>8.07</v>
       </c>
-      <c r="V4" s="4" t="n">
+      <c r="AA4" s="4" t="n">
         <v>1.25</v>
       </c>
-      <c r="W4" s="4" t="n">
+      <c r="AB4" s="4" t="n">
         <v>0.159324</v>
       </c>
-      <c r="X4" s="4" t="n">
+      <c r="AC4" s="4" t="n">
         <v>0.2125</v>
       </c>
-      <c r="Y4" s="4" t="n">
+      <c r="AD4" s="4" t="n">
         <v>0.2125</v>
       </c>
-      <c r="Z4" s="4" t="inlineStr">
+      <c r="AE4" s="4" t="inlineStr">
         <is>
           <t>🟡 首日上涨，可关注</t>
         </is>
       </c>
-      <c r="AA4" s="4" t="n">
+      <c r="AF4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AB4" s="4" t="n">
+      <c r="AG4" s="4" t="n">
         <v>7.44</v>
       </c>
-      <c r="AC4" s="4" t="n">
+      <c r="AH4" s="4" t="n">
         <v>8.9</v>
       </c>
-      <c r="AD4" s="4" t="n">
+      <c r="AI4" s="4" t="n">
         <v>9.460000000000001</v>
       </c>
-      <c r="AE4" s="4" t="n">
+      <c r="AJ4" s="4" t="n">
         <v>7.53</v>
       </c>
-      <c r="AF4" s="4" t="n">
+      <c r="AK4" s="4" t="n">
         <v>1.6</v>
       </c>
-      <c r="AG4" s="4" t="inlineStr">
+      <c r="AL4" s="4" t="inlineStr">
         <is>
           <t>3日短线计划；T+1看8.50/止损7.72；T+2看8.67/止损7.57；T+3看8.90/止损7.53</t>
         </is>
       </c>
-      <c r="AH4" s="4" t="n">
+      <c r="AM4" s="4" t="n">
         <v>7.72</v>
       </c>
-      <c r="AI4" s="4" t="n">
+      <c r="AN4" s="4" t="n">
         <v>8.5</v>
       </c>
-      <c r="AJ4" s="4" t="inlineStr">
+      <c r="AO4" s="4" t="inlineStr">
         <is>
           <t>T+1：冲到8.50先减仓，跌破7.72止损；若高开低走不恋战</t>
         </is>
       </c>
-      <c r="AK4" s="4" t="n">
+      <c r="AP4" s="4" t="n">
         <v>7.57</v>
       </c>
-      <c r="AL4" s="4" t="n">
+      <c r="AQ4" s="4" t="n">
         <v>8.67</v>
       </c>
-      <c r="AM4" s="4" t="inlineStr">
+      <c r="AR4" s="4" t="inlineStr">
         <is>
           <t>T+2：未突破8.67且量能转弱则减仓，跌破7.57退出</t>
         </is>
       </c>
-      <c r="AN4" s="4" t="n">
+      <c r="AS4" s="4" t="n">
         <v>7.53</v>
       </c>
-      <c r="AO4" s="4" t="n">
+      <c r="AT4" s="4" t="n">
         <v>8.9</v>
       </c>
-      <c r="AP4" s="4" t="inlineStr">
+      <c r="AU4" s="4" t="inlineStr">
         <is>
           <t>T+3：到8.90分批止盈，跌破7.53或MA5失守退出</t>
         </is>
@@ -1811,83 +1915,106 @@
         <v>9.619999999999999</v>
       </c>
       <c r="S5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>近期无重大公告</t>
+        </is>
+      </c>
+      <c r="U5" s="4" t="inlineStr">
+        <is>
+          <t>无两融数据</t>
+        </is>
+      </c>
+      <c r="V5" s="4" t="inlineStr">
+        <is>
+          <t>近期未上龙虎榜</t>
+        </is>
+      </c>
+      <c r="W5" s="4" t="inlineStr">
+        <is>
+          <t>近期无重大公告；无两融数据；近期未上龙虎榜</t>
+        </is>
+      </c>
+      <c r="X5" s="4" t="n">
         <v>36.1</v>
       </c>
-      <c r="T5" s="4" t="n">
+      <c r="Y5" s="4" t="n">
         <v>19.84</v>
       </c>
-      <c r="U5" s="4" t="n">
+      <c r="Z5" s="4" t="n">
         <v>8.32</v>
       </c>
-      <c r="V5" s="4" t="n">
+      <c r="AA5" s="4" t="n">
         <v>1.22</v>
       </c>
-      <c r="W5" s="4" t="n">
+      <c r="AB5" s="4" t="n">
         <v>0.08888699999999999</v>
       </c>
-      <c r="X5" s="4" t="n">
+      <c r="AC5" s="4" t="n">
         <v>0.0375</v>
       </c>
-      <c r="Y5" s="4" t="n">
+      <c r="AD5" s="4" t="n">
         <v>0.0375</v>
       </c>
-      <c r="Z5" s="4" t="inlineStr">
+      <c r="AE5" s="4" t="inlineStr">
         <is>
           <t>🟡 首日上涨，可关注</t>
         </is>
       </c>
-      <c r="AA5" s="4" t="n">
+      <c r="AF5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="AB5" s="4" t="n">
+      <c r="AG5" s="4" t="n">
         <v>8.460000000000001</v>
       </c>
-      <c r="AC5" s="4" t="n">
+      <c r="AH5" s="4" t="n">
         <v>10.35</v>
       </c>
-      <c r="AD5" s="4" t="n">
+      <c r="AI5" s="4" t="n">
         <v>11.6</v>
       </c>
-      <c r="AE5" s="4" t="n">
+      <c r="AJ5" s="4" t="n">
         <v>8.460000000000001</v>
       </c>
-      <c r="AF5" s="4" t="n">
+      <c r="AK5" s="4" t="n">
         <v>1.97</v>
       </c>
-      <c r="AG5" s="4" t="inlineStr">
+      <c r="AL5" s="4" t="inlineStr">
         <is>
           <t>1日短线计划；T+1看9.77/止损8.78；T+2看10.10/止损8.46；T+3看10.35/止损8.46</t>
         </is>
       </c>
-      <c r="AH5" s="4" t="n">
+      <c r="AM5" s="4" t="n">
         <v>8.779999999999999</v>
       </c>
-      <c r="AI5" s="4" t="n">
+      <c r="AN5" s="4" t="n">
         <v>9.77</v>
       </c>
-      <c r="AJ5" s="4" t="inlineStr">
+      <c r="AO5" s="4" t="inlineStr">
         <is>
           <t>T+1：冲到9.77先减仓，跌破8.78止损；若高开低走不恋战</t>
         </is>
       </c>
-      <c r="AK5" s="4" t="n">
+      <c r="AP5" s="4" t="n">
         <v>8.460000000000001</v>
       </c>
-      <c r="AL5" s="4" t="n">
+      <c r="AQ5" s="4" t="n">
         <v>10.1</v>
       </c>
-      <c r="AM5" s="4" t="inlineStr">
+      <c r="AR5" s="4" t="inlineStr">
         <is>
           <t>T+2：未突破10.10且量能转弱则减仓，跌破8.46退出</t>
         </is>
       </c>
-      <c r="AN5" s="4" t="n">
+      <c r="AS5" s="4" t="n">
         <v>8.460000000000001</v>
       </c>
-      <c r="AO5" s="4" t="n">
+      <c r="AT5" s="4" t="n">
         <v>10.35</v>
       </c>
-      <c r="AP5" s="4" t="inlineStr">
+      <c r="AU5" s="4" t="inlineStr">
         <is>
           <t>T+3：到10.35分批止盈，跌破8.46或MA5失守退出</t>
         </is>
@@ -1951,83 +2078,106 @@
         <v>9.31</v>
       </c>
       <c r="S6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>近期无重大公告</t>
+        </is>
+      </c>
+      <c r="U6" s="4" t="inlineStr">
+        <is>
+          <t>无两融数据</t>
+        </is>
+      </c>
+      <c r="V6" s="4" t="inlineStr">
+        <is>
+          <t>近期未上龙虎榜</t>
+        </is>
+      </c>
+      <c r="W6" s="4" t="inlineStr">
+        <is>
+          <t>近期无重大公告；无两融数据；近期未上龙虎榜</t>
+        </is>
+      </c>
+      <c r="X6" s="4" t="n">
         <v>57.4</v>
       </c>
-      <c r="T6" s="4" t="n">
+      <c r="Y6" s="4" t="n">
         <v>55.92</v>
       </c>
-      <c r="U6" s="4" t="n">
+      <c r="Z6" s="4" t="n">
         <v>3.85</v>
       </c>
-      <c r="V6" s="4" t="n">
+      <c r="AA6" s="4" t="n">
         <v>2.62</v>
       </c>
-      <c r="W6" s="4" t="n">
+      <c r="AB6" s="4" t="n">
         <v>0.139329</v>
       </c>
-      <c r="X6" s="4" t="n">
+      <c r="AC6" s="4" t="n">
         <v>0.0688</v>
       </c>
-      <c r="Y6" s="4" t="n">
+      <c r="AD6" s="4" t="n">
         <v>0.0688</v>
       </c>
-      <c r="Z6" s="4" t="inlineStr">
+      <c r="AE6" s="4" t="inlineStr">
         <is>
           <t>🟠 连涨多日，等回调再入</t>
         </is>
       </c>
-      <c r="AA6" s="4" t="n">
+      <c r="AF6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="AB6" s="4" t="n">
+      <c r="AG6" s="4" t="n">
         <v>70.34999999999999</v>
       </c>
-      <c r="AC6" s="4" t="n">
+      <c r="AH6" s="4" t="n">
         <v>84.12</v>
       </c>
-      <c r="AD6" s="4" t="n">
+      <c r="AI6" s="4" t="n">
         <v>89.42</v>
       </c>
-      <c r="AE6" s="4" t="n">
+      <c r="AJ6" s="4" t="n">
         <v>71.23</v>
       </c>
-      <c r="AF6" s="4" t="n">
+      <c r="AK6" s="4" t="n">
         <v>1.6</v>
       </c>
-      <c r="AG6" s="4" t="inlineStr">
+      <c r="AL6" s="4" t="inlineStr">
         <is>
           <t>1日短线计划；T+1看80.42/止损73.00；T+2看82.00/止损70.86；T+3看84.12/止损71.23</t>
         </is>
       </c>
-      <c r="AH6" s="4" t="n">
+      <c r="AM6" s="4" t="n">
         <v>73</v>
       </c>
-      <c r="AI6" s="4" t="n">
+      <c r="AN6" s="4" t="n">
         <v>80.42</v>
       </c>
-      <c r="AJ6" s="4" t="inlineStr">
+      <c r="AO6" s="4" t="inlineStr">
         <is>
           <t>T+1：冲到80.42先减仓，跌破73.00止损；若高开低走不恋战</t>
         </is>
       </c>
-      <c r="AK6" s="4" t="n">
+      <c r="AP6" s="4" t="n">
         <v>70.86</v>
       </c>
-      <c r="AL6" s="4" t="n">
+      <c r="AQ6" s="4" t="n">
         <v>82</v>
       </c>
-      <c r="AM6" s="4" t="inlineStr">
+      <c r="AR6" s="4" t="inlineStr">
         <is>
           <t>T+2：未突破82.00且量能转弱则减仓，跌破70.86退出</t>
         </is>
       </c>
-      <c r="AN6" s="4" t="n">
+      <c r="AS6" s="4" t="n">
         <v>71.23</v>
       </c>
-      <c r="AO6" s="4" t="n">
+      <c r="AT6" s="4" t="n">
         <v>84.12</v>
       </c>
-      <c r="AP6" s="4" t="inlineStr">
+      <c r="AU6" s="4" t="inlineStr">
         <is>
           <t>T+3：到84.12分批止盈，跌破71.23或MA5失守退出</t>
         </is>
@@ -2091,83 +2241,106 @@
         <v>9.119999999999999</v>
       </c>
       <c r="S7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="4" t="inlineStr">
+        <is>
+          <t>近期无重大公告</t>
+        </is>
+      </c>
+      <c r="U7" s="4" t="inlineStr">
+        <is>
+          <t>无两融数据</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>近期未上龙虎榜</t>
+        </is>
+      </c>
+      <c r="W7" s="4" t="inlineStr">
+        <is>
+          <t>近期无重大公告；无两融数据；近期未上龙虎榜</t>
+        </is>
+      </c>
+      <c r="X7" s="4" t="n">
         <v>44.9</v>
       </c>
-      <c r="T7" s="4" t="n">
+      <c r="Y7" s="4" t="n">
         <v>37.03</v>
       </c>
-      <c r="U7" s="4" t="n">
+      <c r="Z7" s="4" t="n">
         <v>10.39</v>
       </c>
-      <c r="V7" s="4" t="n">
+      <c r="AA7" s="4" t="n">
         <v>1.33</v>
       </c>
-      <c r="W7" s="4" t="n">
+      <c r="AB7" s="4" t="n">
         <v>0.115259</v>
       </c>
-      <c r="X7" s="4" t="n">
+      <c r="AC7" s="4" t="n">
         <v>0.08749999999999999</v>
       </c>
-      <c r="Y7" s="4" t="n">
+      <c r="AD7" s="4" t="n">
         <v>0.08749999999999999</v>
       </c>
-      <c r="Z7" s="4" t="inlineStr">
+      <c r="AE7" s="4" t="inlineStr">
         <is>
           <t>🟡 首日上涨，可关注</t>
         </is>
       </c>
-      <c r="AA7" s="4" t="n">
+      <c r="AF7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AB7" s="4" t="n">
+      <c r="AG7" s="4" t="n">
         <v>10.95</v>
       </c>
-      <c r="AC7" s="4" t="n">
+      <c r="AH7" s="4" t="n">
         <v>13.09</v>
       </c>
-      <c r="AD7" s="4" t="n">
+      <c r="AI7" s="4" t="n">
         <v>13.95</v>
       </c>
-      <c r="AE7" s="4" t="n">
+      <c r="AJ7" s="4" t="n">
         <v>10.95</v>
       </c>
-      <c r="AF7" s="4" t="n">
+      <c r="AK7" s="4" t="n">
         <v>1.6</v>
       </c>
-      <c r="AG7" s="4" t="inlineStr">
+      <c r="AL7" s="4" t="inlineStr">
         <is>
           <t>3日短线计划；T+1看12.51/止损11.36；T+2看12.76/止损10.95；T+3看13.09/止损10.95</t>
         </is>
       </c>
-      <c r="AH7" s="4" t="n">
+      <c r="AM7" s="4" t="n">
         <v>11.36</v>
       </c>
-      <c r="AI7" s="4" t="n">
+      <c r="AN7" s="4" t="n">
         <v>12.51</v>
       </c>
-      <c r="AJ7" s="4" t="inlineStr">
+      <c r="AO7" s="4" t="inlineStr">
         <is>
           <t>T+1：冲到12.51先减仓，跌破11.36止损；若高开低走不恋战</t>
         </is>
       </c>
-      <c r="AK7" s="4" t="n">
+      <c r="AP7" s="4" t="n">
         <v>10.95</v>
       </c>
-      <c r="AL7" s="4" t="n">
+      <c r="AQ7" s="4" t="n">
         <v>12.76</v>
       </c>
-      <c r="AM7" s="4" t="inlineStr">
+      <c r="AR7" s="4" t="inlineStr">
         <is>
           <t>T+2：未突破12.76且量能转弱则减仓，跌破10.95退出</t>
         </is>
       </c>
-      <c r="AN7" s="4" t="n">
+      <c r="AS7" s="4" t="n">
         <v>10.95</v>
       </c>
-      <c r="AO7" s="4" t="n">
+      <c r="AT7" s="4" t="n">
         <v>13.09</v>
       </c>
-      <c r="AP7" s="4" t="inlineStr">
+      <c r="AU7" s="4" t="inlineStr">
         <is>
           <t>T+3：到13.09分批止盈，跌破10.95或MA5失守退出</t>
         </is>
@@ -2231,83 +2404,106 @@
         <v>7.38</v>
       </c>
       <c r="S8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>近期无重大公告</t>
+        </is>
+      </c>
+      <c r="U8" s="4" t="inlineStr">
+        <is>
+          <t>无两融数据</t>
+        </is>
+      </c>
+      <c r="V8" s="4" t="inlineStr">
+        <is>
+          <t>近期未上龙虎榜</t>
+        </is>
+      </c>
+      <c r="W8" s="4" t="inlineStr">
+        <is>
+          <t>近期无重大公告；无两融数据；近期未上龙虎榜</t>
+        </is>
+      </c>
+      <c r="X8" s="4" t="n">
         <v>38.6</v>
       </c>
-      <c r="T8" s="4" t="n">
+      <c r="Y8" s="4" t="n">
         <v>35.25</v>
       </c>
-      <c r="U8" s="4" t="n">
+      <c r="Z8" s="4" t="n">
         <v>11.74</v>
       </c>
-      <c r="V8" s="4" t="n">
+      <c r="AA8" s="4" t="n">
         <v>1.21</v>
       </c>
-      <c r="W8" s="4" t="n">
+      <c r="AB8" s="4" t="n">
         <v>0.145687</v>
       </c>
-      <c r="X8" s="4" t="n">
+      <c r="AC8" s="4" t="n">
         <v>0.2625</v>
       </c>
-      <c r="Y8" s="4" t="n">
+      <c r="AD8" s="4" t="n">
         <v>0.2625</v>
       </c>
-      <c r="Z8" s="4" t="inlineStr">
+      <c r="AE8" s="4" t="inlineStr">
         <is>
           <t>🟡 首日上涨，可关注</t>
         </is>
       </c>
-      <c r="AA8" s="4" t="n">
+      <c r="AF8" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AB8" s="4" t="n">
+      <c r="AG8" s="4" t="n">
         <v>6.05</v>
       </c>
-      <c r="AC8" s="4" t="n">
+      <c r="AH8" s="4" t="n">
         <v>7.24</v>
       </c>
-      <c r="AD8" s="4" t="n">
+      <c r="AI8" s="4" t="n">
         <v>7.69</v>
       </c>
-      <c r="AE8" s="4" t="n">
+      <c r="AJ8" s="4" t="n">
         <v>6.08</v>
       </c>
-      <c r="AF8" s="4" t="n">
+      <c r="AK8" s="4" t="n">
         <v>1.6</v>
       </c>
-      <c r="AG8" s="4" t="inlineStr">
+      <c r="AL8" s="4" t="inlineStr">
         <is>
           <t>3日短线计划；T+1看6.92/止损6.28；T+2看7.06/止损6.11；T+3看7.24/止损6.08</t>
         </is>
       </c>
-      <c r="AH8" s="4" t="n">
+      <c r="AM8" s="4" t="n">
         <v>6.28</v>
       </c>
-      <c r="AI8" s="4" t="n">
+      <c r="AN8" s="4" t="n">
         <v>6.92</v>
       </c>
-      <c r="AJ8" s="4" t="inlineStr">
+      <c r="AO8" s="4" t="inlineStr">
         <is>
           <t>T+1：冲到6.92先减仓，跌破6.28止损；若高开低走不恋战</t>
         </is>
       </c>
-      <c r="AK8" s="4" t="n">
+      <c r="AP8" s="4" t="n">
         <v>6.11</v>
       </c>
-      <c r="AL8" s="4" t="n">
+      <c r="AQ8" s="4" t="n">
         <v>7.06</v>
       </c>
-      <c r="AM8" s="4" t="inlineStr">
+      <c r="AR8" s="4" t="inlineStr">
         <is>
           <t>T+2：未突破7.06且量能转弱则减仓，跌破6.11退出</t>
         </is>
       </c>
-      <c r="AN8" s="4" t="n">
+      <c r="AS8" s="4" t="n">
         <v>6.08</v>
       </c>
-      <c r="AO8" s="4" t="n">
+      <c r="AT8" s="4" t="n">
         <v>7.24</v>
       </c>
-      <c r="AP8" s="4" t="inlineStr">
+      <c r="AU8" s="4" t="inlineStr">
         <is>
           <t>T+3：到7.24分批止盈，跌破6.08或MA5失守退出</t>
         </is>
@@ -2371,83 +2567,106 @@
         <v>6</v>
       </c>
       <c r="S9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="4" t="inlineStr">
+        <is>
+          <t>近期无重大公告</t>
+        </is>
+      </c>
+      <c r="U9" s="4" t="inlineStr">
+        <is>
+          <t>无两融数据</t>
+        </is>
+      </c>
+      <c r="V9" s="4" t="inlineStr">
+        <is>
+          <t>近期未上龙虎榜</t>
+        </is>
+      </c>
+      <c r="W9" s="4" t="inlineStr">
+        <is>
+          <t>近期无重大公告；无两融数据；近期未上龙虎榜</t>
+        </is>
+      </c>
+      <c r="X9" s="4" t="n">
         <v>35.7</v>
       </c>
-      <c r="T9" s="4" t="n">
+      <c r="Y9" s="4" t="n">
         <v>33.66</v>
       </c>
-      <c r="U9" s="4" t="n">
+      <c r="Z9" s="4" t="n">
         <v>8.9</v>
       </c>
-      <c r="V9" s="4" t="n">
+      <c r="AA9" s="4" t="n">
         <v>1.28</v>
       </c>
-      <c r="W9" s="4" t="n">
+      <c r="AB9" s="4" t="n">
         <v>0.161675</v>
       </c>
-      <c r="X9" s="4" t="n">
+      <c r="AC9" s="4" t="n">
         <v>0.4</v>
       </c>
-      <c r="Y9" s="4" t="n">
+      <c r="AD9" s="4" t="n">
         <v>0.4</v>
       </c>
-      <c r="Z9" s="4" t="inlineStr">
+      <c r="AE9" s="4" t="inlineStr">
         <is>
           <t>🟡 首日上涨，可关注</t>
         </is>
       </c>
-      <c r="AA9" s="4" t="n">
+      <c r="AF9" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AB9" s="4" t="n">
+      <c r="AG9" s="4" t="n">
         <v>12.95</v>
       </c>
-      <c r="AC9" s="4" t="n">
+      <c r="AH9" s="4" t="n">
         <v>15.49</v>
       </c>
-      <c r="AD9" s="4" t="n">
+      <c r="AI9" s="4" t="n">
         <v>16.59</v>
       </c>
-      <c r="AE9" s="4" t="n">
+      <c r="AJ9" s="4" t="n">
         <v>12.95</v>
       </c>
-      <c r="AF9" s="4" t="n">
+      <c r="AK9" s="4" t="n">
         <v>1.6</v>
       </c>
-      <c r="AG9" s="4" t="inlineStr">
+      <c r="AL9" s="4" t="inlineStr">
         <is>
           <t>3日短线计划；T+1看14.81/止损13.44；T+2看15.10/止损12.95；T+3看15.49/止损12.95</t>
         </is>
       </c>
-      <c r="AH9" s="4" t="n">
+      <c r="AM9" s="4" t="n">
         <v>13.44</v>
       </c>
-      <c r="AI9" s="4" t="n">
+      <c r="AN9" s="4" t="n">
         <v>14.81</v>
       </c>
-      <c r="AJ9" s="4" t="inlineStr">
+      <c r="AO9" s="4" t="inlineStr">
         <is>
           <t>T+1：冲到14.81先减仓，跌破13.44止损；若高开低走不恋战</t>
         </is>
       </c>
-      <c r="AK9" s="4" t="n">
+      <c r="AP9" s="4" t="n">
         <v>12.95</v>
       </c>
-      <c r="AL9" s="4" t="n">
+      <c r="AQ9" s="4" t="n">
         <v>15.1</v>
       </c>
-      <c r="AM9" s="4" t="inlineStr">
+      <c r="AR9" s="4" t="inlineStr">
         <is>
           <t>T+2：未突破15.10且量能转弱则减仓，跌破12.95退出</t>
         </is>
       </c>
-      <c r="AN9" s="4" t="n">
+      <c r="AS9" s="4" t="n">
         <v>12.95</v>
       </c>
-      <c r="AO9" s="4" t="n">
+      <c r="AT9" s="4" t="n">
         <v>15.49</v>
       </c>
-      <c r="AP9" s="4" t="inlineStr">
+      <c r="AU9" s="4" t="inlineStr">
         <is>
           <t>T+3：到15.49分批止盈，跌破12.95或MA5失守退出</t>
         </is>
@@ -2511,83 +2730,106 @@
         <v>6.62</v>
       </c>
       <c r="S10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="4" t="inlineStr">
+        <is>
+          <t>近期无重大公告</t>
+        </is>
+      </c>
+      <c r="U10" s="4" t="inlineStr">
+        <is>
+          <t>无两融数据</t>
+        </is>
+      </c>
+      <c r="V10" s="4" t="inlineStr">
+        <is>
+          <t>近期未上龙虎榜</t>
+        </is>
+      </c>
+      <c r="W10" s="4" t="inlineStr">
+        <is>
+          <t>近期无重大公告；无两融数据；近期未上龙虎榜</t>
+        </is>
+      </c>
+      <c r="X10" s="4" t="n">
         <v>59.4</v>
       </c>
-      <c r="T10" s="4" t="n">
+      <c r="Y10" s="4" t="n">
         <v>55.8</v>
       </c>
-      <c r="U10" s="4" t="n">
+      <c r="Z10" s="4" t="n">
         <v>4.6</v>
       </c>
-      <c r="V10" s="4" t="n">
+      <c r="AA10" s="4" t="n">
         <v>1.28</v>
       </c>
-      <c r="W10" s="4" t="n">
+      <c r="AB10" s="4" t="n">
         <v>0.156175</v>
       </c>
-      <c r="X10" s="4" t="n">
+      <c r="AC10" s="4" t="n">
         <v>0.3375</v>
       </c>
-      <c r="Y10" s="4" t="n">
+      <c r="AD10" s="4" t="n">
         <v>0.3375</v>
       </c>
-      <c r="Z10" s="4" t="inlineStr">
+      <c r="AE10" s="4" t="inlineStr">
         <is>
           <t>🟠 远离均线，不宜追高</t>
         </is>
       </c>
-      <c r="AA10" s="4" t="n">
+      <c r="AF10" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="AB10" s="4" t="n">
+      <c r="AG10" s="4" t="n">
         <v>44.42</v>
       </c>
-      <c r="AC10" s="4" t="n">
+      <c r="AH10" s="4" t="n">
         <v>53.11</v>
       </c>
-      <c r="AD10" s="4" t="n">
+      <c r="AI10" s="4" t="n">
         <v>57.87</v>
       </c>
-      <c r="AE10" s="4" t="n">
+      <c r="AJ10" s="4" t="n">
         <v>44.42</v>
       </c>
-      <c r="AF10" s="4" t="n">
+      <c r="AK10" s="4" t="n">
         <v>1.6</v>
       </c>
-      <c r="AG10" s="4" t="inlineStr">
+      <c r="AL10" s="4" t="inlineStr">
         <is>
           <t>1日短线计划；T+1看50.77/止损46.09；T+2看51.81/止损44.42；T+3看53.11/止损44.42</t>
         </is>
       </c>
-      <c r="AH10" s="4" t="n">
+      <c r="AM10" s="4" t="n">
         <v>46.09</v>
       </c>
-      <c r="AI10" s="4" t="n">
+      <c r="AN10" s="4" t="n">
         <v>50.77</v>
       </c>
-      <c r="AJ10" s="4" t="inlineStr">
+      <c r="AO10" s="4" t="inlineStr">
         <is>
           <t>T+1：冲到50.77先减仓，跌破46.09止损；若高开低走不恋战</t>
         </is>
       </c>
-      <c r="AK10" s="4" t="n">
+      <c r="AP10" s="4" t="n">
         <v>44.42</v>
       </c>
-      <c r="AL10" s="4" t="n">
+      <c r="AQ10" s="4" t="n">
         <v>51.81</v>
       </c>
-      <c r="AM10" s="4" t="inlineStr">
+      <c r="AR10" s="4" t="inlineStr">
         <is>
           <t>T+2：未突破51.81且量能转弱则减仓，跌破44.42退出</t>
         </is>
       </c>
-      <c r="AN10" s="4" t="n">
+      <c r="AS10" s="4" t="n">
         <v>44.42</v>
       </c>
-      <c r="AO10" s="4" t="n">
+      <c r="AT10" s="4" t="n">
         <v>53.11</v>
       </c>
-      <c r="AP10" s="4" t="inlineStr">
+      <c r="AU10" s="4" t="inlineStr">
         <is>
           <t>T+3：到53.11分批止盈，跌破44.42或MA5失守退出</t>
         </is>
@@ -2651,83 +2893,106 @@
         <v>9.880000000000001</v>
       </c>
       <c r="S11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="4" t="inlineStr">
+        <is>
+          <t>近期无重大公告</t>
+        </is>
+      </c>
+      <c r="U11" s="4" t="inlineStr">
+        <is>
+          <t>无两融数据</t>
+        </is>
+      </c>
+      <c r="V11" s="4" t="inlineStr">
+        <is>
+          <t>近期未上龙虎榜</t>
+        </is>
+      </c>
+      <c r="W11" s="4" t="inlineStr">
+        <is>
+          <t>近期无重大公告；无两融数据；近期未上龙虎榜</t>
+        </is>
+      </c>
+      <c r="X11" s="4" t="n">
         <v>33.9</v>
       </c>
-      <c r="T11" s="4" t="n">
+      <c r="Y11" s="4" t="n">
         <v>38.9</v>
       </c>
-      <c r="U11" s="4" t="n">
+      <c r="Z11" s="4" t="n">
         <v>13.38</v>
       </c>
-      <c r="V11" s="4" t="n">
+      <c r="AA11" s="4" t="n">
         <v>1.46</v>
       </c>
-      <c r="W11" s="4" t="n">
+      <c r="AB11" s="4" t="n">
         <v>0.00655</v>
       </c>
-      <c r="X11" s="4" t="n">
+      <c r="AC11" s="4" t="n">
         <v>0.0125</v>
       </c>
-      <c r="Y11" s="4" t="n">
+      <c r="AD11" s="4" t="n">
         <v>0.0125</v>
       </c>
-      <c r="Z11" s="4" t="inlineStr">
+      <c r="AE11" s="4" t="inlineStr">
         <is>
           <t>🟡 首日上涨，可关注</t>
         </is>
       </c>
-      <c r="AA11" s="4" t="n">
+      <c r="AF11" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="AB11" s="4" t="n">
+      <c r="AG11" s="4" t="n">
         <v>4.97</v>
       </c>
-      <c r="AC11" s="4" t="n">
+      <c r="AH11" s="4" t="n">
         <v>5.94</v>
       </c>
-      <c r="AD11" s="4" t="n">
+      <c r="AI11" s="4" t="n">
         <v>6.31</v>
       </c>
-      <c r="AE11" s="4" t="n">
+      <c r="AJ11" s="4" t="n">
         <v>5.01</v>
       </c>
-      <c r="AF11" s="4" t="n">
+      <c r="AK11" s="4" t="n">
         <v>1.6</v>
       </c>
-      <c r="AG11" s="4" t="inlineStr">
+      <c r="AL11" s="4" t="inlineStr">
         <is>
           <t>2日短线计划；T+1看5.68/止损5.15；T+2看5.79/止损4.98；T+3看5.94/止损5.01</t>
         </is>
       </c>
-      <c r="AH11" s="4" t="n">
+      <c r="AM11" s="4" t="n">
         <v>5.15</v>
       </c>
-      <c r="AI11" s="4" t="n">
+      <c r="AN11" s="4" t="n">
         <v>5.68</v>
       </c>
-      <c r="AJ11" s="4" t="inlineStr">
+      <c r="AO11" s="4" t="inlineStr">
         <is>
           <t>T+1：冲到5.68先减仓，跌破5.15止损；若高开低走不恋战</t>
         </is>
       </c>
-      <c r="AK11" s="4" t="n">
+      <c r="AP11" s="4" t="n">
         <v>4.98</v>
       </c>
-      <c r="AL11" s="4" t="n">
+      <c r="AQ11" s="4" t="n">
         <v>5.79</v>
       </c>
-      <c r="AM11" s="4" t="inlineStr">
+      <c r="AR11" s="4" t="inlineStr">
         <is>
           <t>T+2：未突破5.79且量能转弱则减仓，跌破4.98退出</t>
         </is>
       </c>
-      <c r="AN11" s="4" t="n">
+      <c r="AS11" s="4" t="n">
         <v>5.01</v>
       </c>
-      <c r="AO11" s="4" t="n">
+      <c r="AT11" s="4" t="n">
         <v>5.94</v>
       </c>
-      <c r="AP11" s="4" t="inlineStr">
+      <c r="AU11" s="4" t="inlineStr">
         <is>
           <t>T+3：到5.94分批止盈，跌破5.01或MA5失守退出</t>
         </is>
@@ -2791,83 +3056,106 @@
         <v>9.31</v>
       </c>
       <c r="S12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="4" t="inlineStr">
+        <is>
+          <t>近期无重大公告</t>
+        </is>
+      </c>
+      <c r="U12" s="4" t="inlineStr">
+        <is>
+          <t>无两融数据</t>
+        </is>
+      </c>
+      <c r="V12" s="4" t="inlineStr">
+        <is>
+          <t>近期未上龙虎榜</t>
+        </is>
+      </c>
+      <c r="W12" s="4" t="inlineStr">
+        <is>
+          <t>近期无重大公告；无两融数据；近期未上龙虎榜</t>
+        </is>
+      </c>
+      <c r="X12" s="4" t="n">
         <v>29.9</v>
       </c>
-      <c r="T12" s="4" t="n">
+      <c r="Y12" s="4" t="n">
         <v>32.92</v>
       </c>
-      <c r="U12" s="4" t="n">
+      <c r="Z12" s="4" t="n">
         <v>11.1</v>
       </c>
-      <c r="V12" s="4" t="n">
+      <c r="AA12" s="4" t="n">
         <v>3.78</v>
       </c>
-      <c r="W12" s="4" t="n">
+      <c r="AB12" s="4" t="n">
         <v>0.100062</v>
       </c>
-      <c r="X12" s="4" t="n">
+      <c r="AC12" s="4" t="n">
         <v>0.0688</v>
       </c>
-      <c r="Y12" s="4" t="n">
+      <c r="AD12" s="4" t="n">
         <v>0.0688</v>
       </c>
-      <c r="Z12" s="4" t="inlineStr">
+      <c r="AE12" s="4" t="inlineStr">
         <is>
           <t>🟡 首日上涨，可关注</t>
         </is>
       </c>
-      <c r="AA12" s="4" t="n">
+      <c r="AF12" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="AB12" s="4" t="n">
+      <c r="AG12" s="4" t="n">
         <v>24.95</v>
       </c>
-      <c r="AC12" s="4" t="n">
+      <c r="AH12" s="4" t="n">
         <v>29.26</v>
       </c>
-      <c r="AD12" s="4" t="n">
+      <c r="AI12" s="4" t="n">
         <v>30.92</v>
       </c>
-      <c r="AE12" s="4" t="n">
+      <c r="AJ12" s="4" t="n">
         <v>25.5</v>
       </c>
-      <c r="AF12" s="4" t="n">
+      <c r="AK12" s="4" t="n">
         <v>1.6</v>
       </c>
-      <c r="AG12" s="4" t="inlineStr">
+      <c r="AL12" s="4" t="inlineStr">
         <is>
           <t>2日短线计划；T+1看28.10/止损25.69；T+2看28.60/止损25.41；T+3看29.26/止损25.50</t>
         </is>
       </c>
-      <c r="AH12" s="4" t="n">
+      <c r="AM12" s="4" t="n">
         <v>25.69</v>
       </c>
-      <c r="AI12" s="4" t="n">
+      <c r="AN12" s="4" t="n">
         <v>28.1</v>
       </c>
-      <c r="AJ12" s="4" t="inlineStr">
+      <c r="AO12" s="4" t="inlineStr">
         <is>
           <t>T+1：冲到28.10先减仓，跌破25.69止损；若高开低走不恋战</t>
         </is>
       </c>
-      <c r="AK12" s="4" t="n">
+      <c r="AP12" s="4" t="n">
         <v>25.41</v>
       </c>
-      <c r="AL12" s="4" t="n">
+      <c r="AQ12" s="4" t="n">
         <v>28.6</v>
       </c>
-      <c r="AM12" s="4" t="inlineStr">
+      <c r="AR12" s="4" t="inlineStr">
         <is>
           <t>T+2：未突破28.60且量能转弱则减仓，跌破25.41退出</t>
         </is>
       </c>
-      <c r="AN12" s="4" t="n">
+      <c r="AS12" s="4" t="n">
         <v>25.5</v>
       </c>
-      <c r="AO12" s="4" t="n">
+      <c r="AT12" s="4" t="n">
         <v>29.26</v>
       </c>
-      <c r="AP12" s="4" t="inlineStr">
+      <c r="AU12" s="4" t="inlineStr">
         <is>
           <t>T+3：到29.26分批止盈，跌破25.50或MA5失守退出</t>
         </is>
@@ -2931,83 +3219,106 @@
         <v>8.880000000000001</v>
       </c>
       <c r="S13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="4" t="inlineStr">
+        <is>
+          <t>近期无重大公告</t>
+        </is>
+      </c>
+      <c r="U13" s="4" t="inlineStr">
+        <is>
+          <t>无两融数据</t>
+        </is>
+      </c>
+      <c r="V13" s="4" t="inlineStr">
+        <is>
+          <t>近期未上龙虎榜</t>
+        </is>
+      </c>
+      <c r="W13" s="4" t="inlineStr">
+        <is>
+          <t>近期无重大公告；无两融数据；近期未上龙虎榜</t>
+        </is>
+      </c>
+      <c r="X13" s="4" t="n">
         <v>53.6</v>
       </c>
-      <c r="T13" s="4" t="n">
+      <c r="Y13" s="4" t="n">
         <v>48.53</v>
       </c>
-      <c r="U13" s="4" t="n">
+      <c r="Z13" s="4" t="n">
         <v>4.93</v>
       </c>
-      <c r="V13" s="4" t="n">
+      <c r="AA13" s="4" t="n">
         <v>2.12</v>
       </c>
-      <c r="W13" s="4" t="n">
+      <c r="AB13" s="4" t="n">
         <v>0.131632</v>
       </c>
-      <c r="X13" s="4" t="n">
+      <c r="AC13" s="4" t="n">
         <v>0.1125</v>
       </c>
-      <c r="Y13" s="4" t="n">
+      <c r="AD13" s="4" t="n">
         <v>0.1125</v>
       </c>
-      <c r="Z13" s="4" t="inlineStr">
+      <c r="AE13" s="4" t="inlineStr">
         <is>
           <t>🟠 远离均线，不宜追高</t>
         </is>
       </c>
-      <c r="AA13" s="4" t="n">
+      <c r="AF13" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="AB13" s="4" t="n">
+      <c r="AG13" s="4" t="n">
         <v>9.44</v>
       </c>
-      <c r="AC13" s="4" t="n">
+      <c r="AH13" s="4" t="n">
         <v>11.29</v>
       </c>
-      <c r="AD13" s="4" t="n">
+      <c r="AI13" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="AE13" s="4" t="n">
+      <c r="AJ13" s="4" t="n">
         <v>9.59</v>
       </c>
-      <c r="AF13" s="4" t="n">
+      <c r="AK13" s="4" t="n">
         <v>1.6</v>
       </c>
-      <c r="AG13" s="4" t="inlineStr">
+      <c r="AL13" s="4" t="inlineStr">
         <is>
           <t>1日短线计划；T+1看10.79/止损9.79；T+2看11.00/止损9.54；T+3看11.29/止损9.59</t>
         </is>
       </c>
-      <c r="AH13" s="4" t="n">
+      <c r="AM13" s="4" t="n">
         <v>9.789999999999999</v>
       </c>
-      <c r="AI13" s="4" t="n">
+      <c r="AN13" s="4" t="n">
         <v>10.79</v>
       </c>
-      <c r="AJ13" s="4" t="inlineStr">
+      <c r="AO13" s="4" t="inlineStr">
         <is>
           <t>T+1：冲到10.79先减仓，跌破9.79止损；若高开低走不恋战</t>
         </is>
       </c>
-      <c r="AK13" s="4" t="n">
+      <c r="AP13" s="4" t="n">
         <v>9.539999999999999</v>
       </c>
-      <c r="AL13" s="4" t="n">
+      <c r="AQ13" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="AM13" s="4" t="inlineStr">
+      <c r="AR13" s="4" t="inlineStr">
         <is>
           <t>T+2：未突破11.00且量能转弱则减仓，跌破9.54退出</t>
         </is>
       </c>
-      <c r="AN13" s="4" t="n">
+      <c r="AS13" s="4" t="n">
         <v>9.59</v>
       </c>
-      <c r="AO13" s="4" t="n">
+      <c r="AT13" s="4" t="n">
         <v>11.29</v>
       </c>
-      <c r="AP13" s="4" t="inlineStr">
+      <c r="AU13" s="4" t="inlineStr">
         <is>
           <t>T+3：到11.29分批止盈，跌破9.59或MA5失守退出</t>
         </is>
@@ -3071,83 +3382,106 @@
         <v>9.5</v>
       </c>
       <c r="S14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="4" t="inlineStr">
+        <is>
+          <t>近期无重大公告</t>
+        </is>
+      </c>
+      <c r="U14" s="4" t="inlineStr">
+        <is>
+          <t>无两融数据</t>
+        </is>
+      </c>
+      <c r="V14" s="4" t="inlineStr">
+        <is>
+          <t>近期未上龙虎榜</t>
+        </is>
+      </c>
+      <c r="W14" s="4" t="inlineStr">
+        <is>
+          <t>近期无重大公告；无两融数据；近期未上龙虎榜</t>
+        </is>
+      </c>
+      <c r="X14" s="4" t="n">
         <v>64.3</v>
       </c>
-      <c r="T14" s="4" t="n">
+      <c r="Y14" s="4" t="n">
         <v>51.55</v>
       </c>
-      <c r="U14" s="4" t="n">
+      <c r="Z14" s="4" t="n">
         <v>4.6</v>
       </c>
-      <c r="V14" s="4" t="n">
+      <c r="AA14" s="4" t="n">
         <v>1.58</v>
       </c>
-      <c r="W14" s="4" t="n">
+      <c r="AB14" s="4" t="n">
         <v>0.08958099999999999</v>
       </c>
-      <c r="X14" s="4" t="n">
+      <c r="AC14" s="4" t="n">
         <v>0.05</v>
       </c>
-      <c r="Y14" s="4" t="n">
+      <c r="AD14" s="4" t="n">
         <v>0.05</v>
       </c>
-      <c r="Z14" s="4" t="inlineStr">
+      <c r="AE14" s="4" t="inlineStr">
         <is>
           <t>🟠 远离均线，不宜追高</t>
         </is>
       </c>
-      <c r="AA14" s="4" t="n">
+      <c r="AF14" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="AB14" s="4" t="n">
+      <c r="AG14" s="4" t="n">
         <v>44.16</v>
       </c>
-      <c r="AC14" s="4" t="n">
+      <c r="AH14" s="4" t="n">
         <v>52.8</v>
       </c>
-      <c r="AD14" s="4" t="n">
+      <c r="AI14" s="4" t="n">
         <v>56.87</v>
       </c>
-      <c r="AE14" s="4" t="n">
+      <c r="AJ14" s="4" t="n">
         <v>44.16</v>
       </c>
-      <c r="AF14" s="4" t="n">
+      <c r="AK14" s="4" t="n">
         <v>1.6</v>
       </c>
-      <c r="AG14" s="4" t="inlineStr">
+      <c r="AL14" s="4" t="inlineStr">
         <is>
           <t>1日短线计划；T+1看50.47/止损45.82；T+2看51.47/止损44.16；T+3看52.80/止损44.16</t>
         </is>
       </c>
-      <c r="AH14" s="4" t="n">
+      <c r="AM14" s="4" t="n">
         <v>45.82</v>
       </c>
-      <c r="AI14" s="4" t="n">
+      <c r="AN14" s="4" t="n">
         <v>50.47</v>
       </c>
-      <c r="AJ14" s="4" t="inlineStr">
+      <c r="AO14" s="4" t="inlineStr">
         <is>
           <t>T+1：冲到50.47先减仓，跌破45.82止损；若高开低走不恋战</t>
         </is>
       </c>
-      <c r="AK14" s="4" t="n">
+      <c r="AP14" s="4" t="n">
         <v>44.16</v>
       </c>
-      <c r="AL14" s="4" t="n">
+      <c r="AQ14" s="4" t="n">
         <v>51.47</v>
       </c>
-      <c r="AM14" s="4" t="inlineStr">
+      <c r="AR14" s="4" t="inlineStr">
         <is>
           <t>T+2：未突破51.47且量能转弱则减仓，跌破44.16退出</t>
         </is>
       </c>
-      <c r="AN14" s="4" t="n">
+      <c r="AS14" s="4" t="n">
         <v>44.16</v>
       </c>
-      <c r="AO14" s="4" t="n">
+      <c r="AT14" s="4" t="n">
         <v>52.8</v>
       </c>
-      <c r="AP14" s="4" t="inlineStr">
+      <c r="AU14" s="4" t="inlineStr">
         <is>
           <t>T+3：到52.80分批止盈，跌破44.16或MA5失守退出</t>
         </is>
@@ -3211,83 +3545,106 @@
         <v>7.12</v>
       </c>
       <c r="S15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="4" t="inlineStr">
+        <is>
+          <t>近期无重大公告</t>
+        </is>
+      </c>
+      <c r="U15" s="4" t="inlineStr">
+        <is>
+          <t>无两融数据</t>
+        </is>
+      </c>
+      <c r="V15" s="4" t="inlineStr">
+        <is>
+          <t>近期未上龙虎榜</t>
+        </is>
+      </c>
+      <c r="W15" s="4" t="inlineStr">
+        <is>
+          <t>近期无重大公告；无两融数据；近期未上龙虎榜</t>
+        </is>
+      </c>
+      <c r="X15" s="4" t="n">
         <v>54.8</v>
       </c>
-      <c r="T15" s="4" t="n">
+      <c r="Y15" s="4" t="n">
         <v>46.5</v>
       </c>
-      <c r="U15" s="4" t="n">
+      <c r="Z15" s="4" t="n">
         <v>4.28</v>
       </c>
-      <c r="V15" s="4" t="n">
+      <c r="AA15" s="4" t="n">
         <v>1.23</v>
       </c>
-      <c r="W15" s="4" t="n">
+      <c r="AB15" s="4" t="n">
         <v>0.151</v>
       </c>
-      <c r="X15" s="4" t="n">
+      <c r="AC15" s="4" t="n">
         <v>0.2875</v>
       </c>
-      <c r="Y15" s="4" t="n">
+      <c r="AD15" s="4" t="n">
         <v>0.2875</v>
       </c>
-      <c r="Z15" s="4" t="inlineStr">
+      <c r="AE15" s="4" t="inlineStr">
         <is>
           <t>🟠 远离均线，不宜追高</t>
         </is>
       </c>
-      <c r="AA15" s="4" t="n">
+      <c r="AF15" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="AB15" s="4" t="n">
+      <c r="AG15" s="4" t="n">
         <v>49.48</v>
       </c>
-      <c r="AC15" s="4" t="n">
+      <c r="AH15" s="4" t="n">
         <v>59.16</v>
       </c>
-      <c r="AD15" s="4" t="n">
+      <c r="AI15" s="4" t="n">
         <v>62.99</v>
       </c>
-      <c r="AE15" s="4" t="n">
+      <c r="AJ15" s="4" t="n">
         <v>49.48</v>
       </c>
-      <c r="AF15" s="4" t="n">
+      <c r="AK15" s="4" t="n">
         <v>1.6</v>
       </c>
-      <c r="AG15" s="4" t="inlineStr">
+      <c r="AL15" s="4" t="inlineStr">
         <is>
           <t>1日短线计划；T+1看56.55/止损51.34；T+2看57.67/止损49.48；T+3看59.16/止损49.48</t>
         </is>
       </c>
-      <c r="AH15" s="4" t="n">
+      <c r="AM15" s="4" t="n">
         <v>51.34</v>
       </c>
-      <c r="AI15" s="4" t="n">
+      <c r="AN15" s="4" t="n">
         <v>56.55</v>
       </c>
-      <c r="AJ15" s="4" t="inlineStr">
+      <c r="AO15" s="4" t="inlineStr">
         <is>
           <t>T+1：冲到56.55先减仓，跌破51.34止损；若高开低走不恋战</t>
         </is>
       </c>
-      <c r="AK15" s="4" t="n">
+      <c r="AP15" s="4" t="n">
         <v>49.48</v>
       </c>
-      <c r="AL15" s="4" t="n">
+      <c r="AQ15" s="4" t="n">
         <v>57.67</v>
       </c>
-      <c r="AM15" s="4" t="inlineStr">
+      <c r="AR15" s="4" t="inlineStr">
         <is>
           <t>T+2：未突破57.67且量能转弱则减仓，跌破49.48退出</t>
         </is>
       </c>
-      <c r="AN15" s="4" t="n">
+      <c r="AS15" s="4" t="n">
         <v>49.48</v>
       </c>
-      <c r="AO15" s="4" t="n">
+      <c r="AT15" s="4" t="n">
         <v>59.16</v>
       </c>
-      <c r="AP15" s="4" t="inlineStr">
+      <c r="AU15" s="4" t="inlineStr">
         <is>
           <t>T+3：到59.16分批止盈，跌破49.48或MA5失守退出</t>
         </is>
@@ -3351,83 +3708,106 @@
         <v>6.12</v>
       </c>
       <c r="S16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="4" t="inlineStr">
+        <is>
+          <t>近期无重大公告</t>
+        </is>
+      </c>
+      <c r="U16" s="4" t="inlineStr">
+        <is>
+          <t>无两融数据</t>
+        </is>
+      </c>
+      <c r="V16" s="4" t="inlineStr">
+        <is>
+          <t>近期未上龙虎榜</t>
+        </is>
+      </c>
+      <c r="W16" s="4" t="inlineStr">
+        <is>
+          <t>近期无重大公告；无两融数据；近期未上龙虎榜</t>
+        </is>
+      </c>
+      <c r="X16" s="4" t="n">
         <v>46.9</v>
       </c>
-      <c r="T16" s="4" t="n">
+      <c r="Y16" s="4" t="n">
         <v>37.32</v>
       </c>
-      <c r="U16" s="4" t="n">
+      <c r="Z16" s="4" t="n">
         <v>9.65</v>
       </c>
-      <c r="V16" s="4" t="n">
+      <c r="AA16" s="4" t="n">
         <v>1.38</v>
       </c>
-      <c r="W16" s="4" t="n">
+      <c r="AB16" s="4" t="n">
         <v>0.150034</v>
       </c>
-      <c r="X16" s="4" t="n">
+      <c r="AC16" s="4" t="n">
         <v>0.3875</v>
       </c>
-      <c r="Y16" s="4" t="n">
+      <c r="AD16" s="4" t="n">
         <v>0.3875</v>
       </c>
-      <c r="Z16" s="4" t="inlineStr">
+      <c r="AE16" s="4" t="inlineStr">
         <is>
           <t>🟡 首日上涨，可关注</t>
         </is>
       </c>
-      <c r="AA16" s="4" t="n">
+      <c r="AF16" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AB16" s="4" t="n">
+      <c r="AG16" s="4" t="n">
         <v>3.34</v>
       </c>
-      <c r="AC16" s="4" t="n">
+      <c r="AH16" s="4" t="n">
         <v>3.99</v>
       </c>
-      <c r="AD16" s="4" t="n">
+      <c r="AI16" s="4" t="n">
         <v>4.24</v>
       </c>
-      <c r="AE16" s="4" t="n">
+      <c r="AJ16" s="4" t="n">
         <v>3.4</v>
       </c>
-      <c r="AF16" s="4" t="n">
+      <c r="AK16" s="4" t="n">
         <v>1.6</v>
       </c>
-      <c r="AG16" s="4" t="inlineStr">
+      <c r="AL16" s="4" t="inlineStr">
         <is>
           <t>3日短线计划；T+1看3.82/止损3.46；T+2看3.89/止损3.39；T+3看3.99/止损3.40</t>
         </is>
       </c>
-      <c r="AH16" s="4" t="n">
+      <c r="AM16" s="4" t="n">
         <v>3.46</v>
       </c>
-      <c r="AI16" s="4" t="n">
+      <c r="AN16" s="4" t="n">
         <v>3.82</v>
       </c>
-      <c r="AJ16" s="4" t="inlineStr">
+      <c r="AO16" s="4" t="inlineStr">
         <is>
           <t>T+1：冲到3.82先减仓，跌破3.46止损；若高开低走不恋战</t>
         </is>
       </c>
-      <c r="AK16" s="4" t="n">
+      <c r="AP16" s="4" t="n">
         <v>3.39</v>
       </c>
-      <c r="AL16" s="4" t="n">
+      <c r="AQ16" s="4" t="n">
         <v>3.89</v>
       </c>
-      <c r="AM16" s="4" t="inlineStr">
+      <c r="AR16" s="4" t="inlineStr">
         <is>
           <t>T+2：未突破3.89且量能转弱则减仓，跌破3.39退出</t>
         </is>
       </c>
-      <c r="AN16" s="4" t="n">
+      <c r="AS16" s="4" t="n">
         <v>3.4</v>
       </c>
-      <c r="AO16" s="4" t="n">
+      <c r="AT16" s="4" t="n">
         <v>3.99</v>
       </c>
-      <c r="AP16" s="4" t="inlineStr">
+      <c r="AU16" s="4" t="inlineStr">
         <is>
           <t>T+3：到3.99分批止盈，跌破3.40或MA5失守退出</t>
         </is>
@@ -3491,83 +3871,106 @@
         <v>6.75</v>
       </c>
       <c r="S17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="4" t="inlineStr">
+        <is>
+          <t>近期无重大公告</t>
+        </is>
+      </c>
+      <c r="U17" s="4" t="inlineStr">
+        <is>
+          <t>无两融数据</t>
+        </is>
+      </c>
+      <c r="V17" s="4" t="inlineStr">
+        <is>
+          <t>近期未上龙虎榜</t>
+        </is>
+      </c>
+      <c r="W17" s="4" t="inlineStr">
+        <is>
+          <t>近期无重大公告；无两融数据；近期未上龙虎榜</t>
+        </is>
+      </c>
+      <c r="X17" s="4" t="n">
         <v>62.3</v>
       </c>
-      <c r="T17" s="4" t="n">
+      <c r="Y17" s="4" t="n">
         <v>32.26</v>
       </c>
-      <c r="U17" s="4" t="n">
+      <c r="Z17" s="4" t="n">
         <v>6.06</v>
       </c>
-      <c r="V17" s="4" t="n">
+      <c r="AA17" s="4" t="n">
         <v>1.24</v>
       </c>
-      <c r="W17" s="4" t="n">
+      <c r="AB17" s="4" t="n">
         <v>0.09954300000000001</v>
       </c>
-      <c r="X17" s="4" t="n">
+      <c r="AC17" s="4" t="n">
         <v>0.325</v>
       </c>
-      <c r="Y17" s="4" t="n">
+      <c r="AD17" s="4" t="n">
         <v>0.325</v>
       </c>
-      <c r="Z17" s="4" t="inlineStr">
+      <c r="AE17" s="4" t="inlineStr">
         <is>
           <t>🟡 首日上涨，可关注</t>
         </is>
       </c>
-      <c r="AA17" s="4" t="n">
+      <c r="AF17" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="AB17" s="4" t="n">
+      <c r="AG17" s="4" t="n">
         <v>60.23</v>
       </c>
-      <c r="AC17" s="4" t="n">
+      <c r="AH17" s="4" t="n">
         <v>72.01000000000001</v>
       </c>
-      <c r="AD17" s="4" t="n">
+      <c r="AI17" s="4" t="n">
         <v>78.61</v>
       </c>
-      <c r="AE17" s="4" t="n">
+      <c r="AJ17" s="4" t="n">
         <v>60.78</v>
       </c>
-      <c r="AF17" s="4" t="n">
+      <c r="AK17" s="4" t="n">
         <v>1.6</v>
       </c>
-      <c r="AG17" s="4" t="inlineStr">
+      <c r="AL17" s="4" t="inlineStr">
         <is>
           <t>1日短线计划；T+1看68.84/止损62.49；T+2看70.30/止损61.09；T+3看72.01/止损60.78</t>
         </is>
       </c>
-      <c r="AH17" s="4" t="n">
+      <c r="AM17" s="4" t="n">
         <v>62.49</v>
       </c>
-      <c r="AI17" s="4" t="n">
+      <c r="AN17" s="4" t="n">
         <v>68.84</v>
       </c>
-      <c r="AJ17" s="4" t="inlineStr">
+      <c r="AO17" s="4" t="inlineStr">
         <is>
           <t>T+1：冲到68.84先减仓，跌破62.49止损；若高开低走不恋战</t>
         </is>
       </c>
-      <c r="AK17" s="4" t="n">
+      <c r="AP17" s="4" t="n">
         <v>61.09</v>
       </c>
-      <c r="AL17" s="4" t="n">
+      <c r="AQ17" s="4" t="n">
         <v>70.3</v>
       </c>
-      <c r="AM17" s="4" t="inlineStr">
+      <c r="AR17" s="4" t="inlineStr">
         <is>
           <t>T+2：未突破70.30且量能转弱则减仓，跌破61.09退出</t>
         </is>
       </c>
-      <c r="AN17" s="4" t="n">
+      <c r="AS17" s="4" t="n">
         <v>60.78</v>
       </c>
-      <c r="AO17" s="4" t="n">
+      <c r="AT17" s="4" t="n">
         <v>72.01000000000001</v>
       </c>
-      <c r="AP17" s="4" t="inlineStr">
+      <c r="AU17" s="4" t="inlineStr">
         <is>
           <t>T+3：到72.01分批止盈，跌破60.78或MA5失守退出</t>
         </is>
@@ -3631,83 +4034,106 @@
         <v>8</v>
       </c>
       <c r="S18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="4" t="inlineStr">
+        <is>
+          <t>近期无重大公告</t>
+        </is>
+      </c>
+      <c r="U18" s="4" t="inlineStr">
+        <is>
+          <t>无两融数据</t>
+        </is>
+      </c>
+      <c r="V18" s="4" t="inlineStr">
+        <is>
+          <t>近期未上龙虎榜</t>
+        </is>
+      </c>
+      <c r="W18" s="4" t="inlineStr">
+        <is>
+          <t>近期无重大公告；无两融数据；近期未上龙虎榜</t>
+        </is>
+      </c>
+      <c r="X18" s="4" t="n">
         <v>43.7</v>
       </c>
-      <c r="T18" s="4" t="n">
+      <c r="Y18" s="4" t="n">
         <v>39.95</v>
       </c>
-      <c r="U18" s="4" t="n">
+      <c r="Z18" s="4" t="n">
         <v>7.91</v>
       </c>
-      <c r="V18" s="4" t="n">
+      <c r="AA18" s="4" t="n">
         <v>1.44</v>
       </c>
-      <c r="W18" s="4" t="n">
+      <c r="AB18" s="4" t="n">
         <v>0.193786</v>
       </c>
-      <c r="X18" s="4" t="n">
+      <c r="AC18" s="4" t="n">
         <v>0.2</v>
       </c>
-      <c r="Y18" s="4" t="n">
+      <c r="AD18" s="4" t="n">
         <v>0.2</v>
       </c>
-      <c r="Z18" s="4" t="inlineStr">
+      <c r="AE18" s="4" t="inlineStr">
         <is>
           <t>🟠 远离均线，不宜追高</t>
         </is>
       </c>
-      <c r="AA18" s="4" t="n">
+      <c r="AF18" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="AB18" s="4" t="n">
+      <c r="AG18" s="4" t="n">
         <v>3.12</v>
       </c>
-      <c r="AC18" s="4" t="n">
+      <c r="AH18" s="4" t="n">
         <v>3.73</v>
       </c>
-      <c r="AD18" s="4" t="n">
+      <c r="AI18" s="4" t="n">
         <v>3.96</v>
       </c>
-      <c r="AE18" s="4" t="n">
+      <c r="AJ18" s="4" t="n">
         <v>3.12</v>
       </c>
-      <c r="AF18" s="4" t="n">
+      <c r="AK18" s="4" t="n">
         <v>1.6</v>
       </c>
-      <c r="AG18" s="4" t="inlineStr">
+      <c r="AL18" s="4" t="inlineStr">
         <is>
           <t>1日短线计划；T+1看3.56/止损3.23；T+2看3.63/止损3.12；T+3看3.73/止损3.12</t>
         </is>
       </c>
-      <c r="AH18" s="4" t="n">
+      <c r="AM18" s="4" t="n">
         <v>3.23</v>
       </c>
-      <c r="AI18" s="4" t="n">
+      <c r="AN18" s="4" t="n">
         <v>3.56</v>
       </c>
-      <c r="AJ18" s="4" t="inlineStr">
+      <c r="AO18" s="4" t="inlineStr">
         <is>
           <t>T+1：冲到3.56先减仓，跌破3.23止损；若高开低走不恋战</t>
         </is>
       </c>
-      <c r="AK18" s="4" t="n">
+      <c r="AP18" s="4" t="n">
         <v>3.12</v>
       </c>
-      <c r="AL18" s="4" t="n">
+      <c r="AQ18" s="4" t="n">
         <v>3.63</v>
       </c>
-      <c r="AM18" s="4" t="inlineStr">
+      <c r="AR18" s="4" t="inlineStr">
         <is>
           <t>T+2：未突破3.63且量能转弱则减仓，跌破3.12退出</t>
         </is>
       </c>
-      <c r="AN18" s="4" t="n">
+      <c r="AS18" s="4" t="n">
         <v>3.12</v>
       </c>
-      <c r="AO18" s="4" t="n">
+      <c r="AT18" s="4" t="n">
         <v>3.73</v>
       </c>
-      <c r="AP18" s="4" t="inlineStr">
+      <c r="AU18" s="4" t="inlineStr">
         <is>
           <t>T+3：到3.73分批止盈，跌破3.12或MA5失守退出</t>
         </is>
@@ -3771,83 +4197,106 @@
         <v>8.380000000000001</v>
       </c>
       <c r="S19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="4" t="inlineStr">
+        <is>
+          <t>近期无重大公告</t>
+        </is>
+      </c>
+      <c r="U19" s="4" t="inlineStr">
+        <is>
+          <t>无两融数据</t>
+        </is>
+      </c>
+      <c r="V19" s="4" t="inlineStr">
+        <is>
+          <t>近期未上龙虎榜</t>
+        </is>
+      </c>
+      <c r="W19" s="4" t="inlineStr">
+        <is>
+          <t>近期无重大公告；无两融数据；近期未上龙虎榜</t>
+        </is>
+      </c>
+      <c r="X19" s="4" t="n">
         <v>42.2</v>
       </c>
-      <c r="T19" s="4" t="n">
+      <c r="Y19" s="4" t="n">
         <v>38.71</v>
       </c>
-      <c r="U19" s="4" t="n">
+      <c r="Z19" s="4" t="n">
         <v>8.49</v>
       </c>
-      <c r="V19" s="4" t="n">
+      <c r="AA19" s="4" t="n">
         <v>1.53</v>
       </c>
-      <c r="W19" s="4" t="n">
+      <c r="AB19" s="4" t="n">
         <v>0.168841</v>
       </c>
-      <c r="X19" s="4" t="n">
+      <c r="AC19" s="4" t="n">
         <v>0.1625</v>
       </c>
-      <c r="Y19" s="4" t="n">
+      <c r="AD19" s="4" t="n">
         <v>0.1625</v>
       </c>
-      <c r="Z19" s="4" t="inlineStr">
+      <c r="AE19" s="4" t="inlineStr">
         <is>
           <t>🟠 远离均线，不宜追高</t>
         </is>
       </c>
-      <c r="AA19" s="4" t="n">
+      <c r="AF19" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="AB19" s="4" t="n">
+      <c r="AG19" s="4" t="n">
         <v>19.04</v>
       </c>
-      <c r="AC19" s="4" t="n">
+      <c r="AH19" s="4" t="n">
         <v>22.76</v>
       </c>
-      <c r="AD19" s="4" t="n">
+      <c r="AI19" s="4" t="n">
         <v>24.2</v>
       </c>
-      <c r="AE19" s="4" t="n">
+      <c r="AJ19" s="4" t="n">
         <v>19.14</v>
       </c>
-      <c r="AF19" s="4" t="n">
+      <c r="AK19" s="4" t="n">
         <v>1.6</v>
       </c>
-      <c r="AG19" s="4" t="inlineStr">
+      <c r="AL19" s="4" t="inlineStr">
         <is>
           <t>1日短线计划；T+1看21.76/止损19.75；T+2看22.19/止损19.04；T+3看22.76/止损19.14</t>
         </is>
       </c>
-      <c r="AH19" s="4" t="n">
+      <c r="AM19" s="4" t="n">
         <v>19.75</v>
       </c>
-      <c r="AI19" s="4" t="n">
+      <c r="AN19" s="4" t="n">
         <v>21.76</v>
       </c>
-      <c r="AJ19" s="4" t="inlineStr">
+      <c r="AO19" s="4" t="inlineStr">
         <is>
           <t>T+1：冲到21.76先减仓，跌破19.75止损；若高开低走不恋战</t>
         </is>
       </c>
-      <c r="AK19" s="4" t="n">
+      <c r="AP19" s="4" t="n">
         <v>19.04</v>
       </c>
-      <c r="AL19" s="4" t="n">
+      <c r="AQ19" s="4" t="n">
         <v>22.19</v>
       </c>
-      <c r="AM19" s="4" t="inlineStr">
+      <c r="AR19" s="4" t="inlineStr">
         <is>
           <t>T+2：未突破22.19且量能转弱则减仓，跌破19.04退出</t>
         </is>
       </c>
-      <c r="AN19" s="4" t="n">
+      <c r="AS19" s="4" t="n">
         <v>19.14</v>
       </c>
-      <c r="AO19" s="4" t="n">
+      <c r="AT19" s="4" t="n">
         <v>22.76</v>
       </c>
-      <c r="AP19" s="4" t="inlineStr">
+      <c r="AU19" s="4" t="inlineStr">
         <is>
           <t>T+3：到22.76分批止盈，跌破19.14或MA5失守退出</t>
         </is>
@@ -3911,83 +4360,106 @@
         <v>5.62</v>
       </c>
       <c r="S20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="4" t="inlineStr">
+        <is>
+          <t>近期无重大公告</t>
+        </is>
+      </c>
+      <c r="U20" s="4" t="inlineStr">
+        <is>
+          <t>无两融数据</t>
+        </is>
+      </c>
+      <c r="V20" s="4" t="inlineStr">
+        <is>
+          <t>近期未上龙虎榜</t>
+        </is>
+      </c>
+      <c r="W20" s="4" t="inlineStr">
+        <is>
+          <t>近期无重大公告；无两融数据；近期未上龙虎榜</t>
+        </is>
+      </c>
+      <c r="X20" s="4" t="n">
         <v>36.9</v>
       </c>
-      <c r="T20" s="4" t="n">
+      <c r="Y20" s="4" t="n">
         <v>31.6</v>
       </c>
-      <c r="U20" s="4" t="n">
+      <c r="Z20" s="4" t="n">
         <v>12.91</v>
       </c>
-      <c r="V20" s="4" t="n">
+      <c r="AA20" s="4" t="n">
         <v>1.21</v>
       </c>
-      <c r="W20" s="4" t="n">
+      <c r="AB20" s="4" t="n">
         <v>0.120918</v>
       </c>
-      <c r="X20" s="4" t="n">
+      <c r="AC20" s="4" t="n">
         <v>0.4375</v>
       </c>
-      <c r="Y20" s="4" t="n">
+      <c r="AD20" s="4" t="n">
         <v>0.4375</v>
       </c>
-      <c r="Z20" s="4" t="inlineStr">
+      <c r="AE20" s="4" t="inlineStr">
         <is>
           <t>🟡 首日上涨，可关注</t>
         </is>
       </c>
-      <c r="AA20" s="4" t="n">
+      <c r="AF20" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AB20" s="4" t="n">
+      <c r="AG20" s="4" t="n">
         <v>27.3</v>
       </c>
-      <c r="AC20" s="4" t="n">
+      <c r="AH20" s="4" t="n">
         <v>31.66</v>
       </c>
-      <c r="AD20" s="4" t="n">
+      <c r="AI20" s="4" t="n">
         <v>33.34</v>
       </c>
-      <c r="AE20" s="4" t="n">
+      <c r="AJ20" s="4" t="n">
         <v>27.86</v>
       </c>
-      <c r="AF20" s="4" t="n">
+      <c r="AK20" s="4" t="n">
         <v>1.6</v>
       </c>
-      <c r="AG20" s="4" t="inlineStr">
+      <c r="AL20" s="4" t="inlineStr">
         <is>
           <t>3日短线计划；T+1看30.49/止损28.05；T+2看30.99/止损27.77；T+3看31.66/止损27.86</t>
         </is>
       </c>
-      <c r="AH20" s="4" t="n">
+      <c r="AM20" s="4" t="n">
         <v>28.05</v>
       </c>
-      <c r="AI20" s="4" t="n">
+      <c r="AN20" s="4" t="n">
         <v>30.49</v>
       </c>
-      <c r="AJ20" s="4" t="inlineStr">
+      <c r="AO20" s="4" t="inlineStr">
         <is>
           <t>T+1：冲到30.49先减仓，跌破28.05止损；若高开低走不恋战</t>
         </is>
       </c>
-      <c r="AK20" s="4" t="n">
+      <c r="AP20" s="4" t="n">
         <v>27.77</v>
       </c>
-      <c r="AL20" s="4" t="n">
+      <c r="AQ20" s="4" t="n">
         <v>30.99</v>
       </c>
-      <c r="AM20" s="4" t="inlineStr">
+      <c r="AR20" s="4" t="inlineStr">
         <is>
           <t>T+2：未突破30.99且量能转弱则减仓，跌破27.77退出</t>
         </is>
       </c>
-      <c r="AN20" s="4" t="n">
+      <c r="AS20" s="4" t="n">
         <v>27.86</v>
       </c>
-      <c r="AO20" s="4" t="n">
+      <c r="AT20" s="4" t="n">
         <v>31.66</v>
       </c>
-      <c r="AP20" s="4" t="inlineStr">
+      <c r="AU20" s="4" t="inlineStr">
         <is>
           <t>T+3：到31.66分批止盈，跌破27.86或MA5失守退出</t>
         </is>
@@ -4051,90 +4523,113 @@
         <v>8.5</v>
       </c>
       <c r="S21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="4" t="inlineStr">
+        <is>
+          <t>近期无重大公告</t>
+        </is>
+      </c>
+      <c r="U21" s="4" t="inlineStr">
+        <is>
+          <t>无两融数据</t>
+        </is>
+      </c>
+      <c r="V21" s="4" t="inlineStr">
+        <is>
+          <t>近期未上龙虎榜</t>
+        </is>
+      </c>
+      <c r="W21" s="4" t="inlineStr">
+        <is>
+          <t>近期无重大公告；无两融数据；近期未上龙虎榜</t>
+        </is>
+      </c>
+      <c r="X21" s="4" t="n">
         <v>53.8</v>
       </c>
-      <c r="T21" s="4" t="n">
+      <c r="Y21" s="4" t="n">
         <v>48.86</v>
       </c>
-      <c r="U21" s="4" t="n">
+      <c r="Z21" s="4" t="n">
         <v>5.38</v>
       </c>
-      <c r="V21" s="4" t="n">
+      <c r="AA21" s="4" t="n">
         <v>2.41</v>
       </c>
-      <c r="W21" s="4" t="n">
+      <c r="AB21" s="4" t="n">
         <v>0.103408</v>
       </c>
-      <c r="X21" s="4" t="n">
+      <c r="AC21" s="4" t="n">
         <v>0.15</v>
       </c>
-      <c r="Y21" s="4" t="n">
+      <c r="AD21" s="4" t="n">
         <v>0.15</v>
       </c>
-      <c r="Z21" s="4" t="inlineStr">
+      <c r="AE21" s="4" t="inlineStr">
         <is>
           <t>🟠 远离均线，不宜追高</t>
         </is>
       </c>
-      <c r="AA21" s="4" t="n">
+      <c r="AF21" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="AB21" s="4" t="n">
+      <c r="AG21" s="4" t="n">
         <v>15.83</v>
       </c>
-      <c r="AC21" s="4" t="n">
+      <c r="AH21" s="4" t="n">
         <v>18.93</v>
       </c>
-      <c r="AD21" s="4" t="n">
+      <c r="AI21" s="4" t="n">
         <v>20.12</v>
       </c>
-      <c r="AE21" s="4" t="n">
+      <c r="AJ21" s="4" t="n">
         <v>15.93</v>
       </c>
-      <c r="AF21" s="4" t="n">
+      <c r="AK21" s="4" t="n">
         <v>1.6</v>
       </c>
-      <c r="AG21" s="4" t="inlineStr">
+      <c r="AL21" s="4" t="inlineStr">
         <is>
           <t>1日短线计划；T+1看18.09/止损16.42；T+2看18.45/止损15.84；T+3看18.93/止损15.93</t>
         </is>
       </c>
-      <c r="AH21" s="4" t="n">
+      <c r="AM21" s="4" t="n">
         <v>16.42</v>
       </c>
-      <c r="AI21" s="4" t="n">
+      <c r="AN21" s="4" t="n">
         <v>18.09</v>
       </c>
-      <c r="AJ21" s="4" t="inlineStr">
+      <c r="AO21" s="4" t="inlineStr">
         <is>
           <t>T+1：冲到18.09先减仓，跌破16.42止损；若高开低走不恋战</t>
         </is>
       </c>
-      <c r="AK21" s="4" t="n">
+      <c r="AP21" s="4" t="n">
         <v>15.84</v>
       </c>
-      <c r="AL21" s="4" t="n">
+      <c r="AQ21" s="4" t="n">
         <v>18.45</v>
       </c>
-      <c r="AM21" s="4" t="inlineStr">
+      <c r="AR21" s="4" t="inlineStr">
         <is>
           <t>T+2：未突破18.45且量能转弱则减仓，跌破15.84退出</t>
         </is>
       </c>
-      <c r="AN21" s="4" t="n">
+      <c r="AS21" s="4" t="n">
         <v>15.93</v>
       </c>
-      <c r="AO21" s="4" t="n">
+      <c r="AT21" s="4" t="n">
         <v>18.93</v>
       </c>
-      <c r="AP21" s="4" t="inlineStr">
+      <c r="AU21" s="4" t="inlineStr">
         <is>
           <t>T+3：到18.93分批止盈，跌破15.93或MA5失守退出</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP21"/>
+  <autoFilter ref="A1:AU21"/>
   <conditionalFormatting sqref="G2:G21">
     <cfRule type="colorScale" priority="1">
       <colorScale>
@@ -4155,7 +4650,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S21">
+  <conditionalFormatting sqref="X2:X21">
     <cfRule type="dataBar" priority="4">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -4164,7 +4659,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V21">
+  <conditionalFormatting sqref="AA2:AA21">
     <cfRule type="dataBar" priority="5">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -4635,7 +5130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4693,17 +5188,17 @@
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>初始股票池</t>
+          <t>初始股票池（当日缓存）</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>5528</v>
+        <v>2125</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>5528</v>
+        <v>2125</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>5528</v>
+        <v>2125</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>1</v>
@@ -4712,235 +5207,235 @@
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>去除 ST</t>
+          <t>最终股票池（当日缓存）</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>5528</v>
+        <v>2125</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>5299</v>
+        <v>2125</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>5299</v>
+        <v>2125</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.9586</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>去除北交所</t>
+          <t>MA 条件</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>5299</v>
+        <v>2123</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>4982</v>
+        <v>219</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>4982</v>
+        <v>219</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.9402</v>
+        <v>0.1032</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>去除停牌</t>
+          <t>MA20 趋势持续性</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>4982</v>
+        <v>2123</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4975</v>
+        <v>63</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>4975</v>
+        <v>63</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.9986</v>
+        <v>0.0297</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>保留沪深主板</t>
+          <t>DMI 条件</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>4975</v>
+        <v>2123</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>2125</v>
+        <v>445</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>2125</v>
+        <v>445</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.4271</v>
+        <v>0.2096</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>MA 条件</t>
+          <t>成交量条件</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>2123</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>219</v>
+        <v>424</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>219</v>
+        <v>424</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.1032</v>
+        <v>0.1997</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>MA20 趋势持续性</t>
+          <t>EXPMA 条件</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
         <v>2123</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>63</v>
+        <v>430</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>63</v>
+        <v>430</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.0297</v>
+        <v>0.2025</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>DMI 条件</t>
+          <t>MACD 二次金叉条件</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>2123</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>445</v>
+        <v>317</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>445</v>
+        <v>317</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.2096</v>
+        <v>0.1493</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>成交量条件</t>
+          <t>技术条件合计</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
         <v>2123</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>424</v>
+        <v>80</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>424</v>
+        <v>80</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.1997</v>
+        <v>0.0377</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>EXPMA 条件</t>
+          <t>成交额过滤</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>2123</v>
+        <v>80</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>430</v>
+        <v>77</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>430</v>
+        <v>77</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.2025</v>
+        <v>0.9625</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>MACD 二次金叉条件</t>
+          <t>资金净流入条件</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>2123</v>
+        <v>80</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>317</v>
+        <v>77</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>317</v>
+        <v>77</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.1493</v>
+        <v>0.9625</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>技术条件合计</t>
+          <t>板块热度条件</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>2123</v>
+        <v>80</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.0377</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>成交额过滤</t>
+          <t>板块内领涨条件</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
         <v>80</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>77</v>
+        <v>16</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>77</v>
+        <v>16</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.9625</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>资金净流入条件</t>
+          <t>最终股票池</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
@@ -4956,65 +5451,8 @@
         <v>0.9625</v>
       </c>
     </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>板块热度条件</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>板块内领涨条件</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>最终股票池</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>77</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>77</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>0.9625</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:E20"/>
+  <autoFilter ref="A3:E17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/A股每日选股报告页面设计/public/reports/20260625/stock_pick_20260625.xlsx
+++ b/A股每日选股报告页面设计/public/reports/20260625/stock_pick_20260625.xlsx
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>107.01</v>
+        <v>107.81</v>
       </c>
       <c r="C5" s="5" t="inlineStr"/>
       <c r="D5" s="2" t="n"/>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>91.2705</v>
+        <v>91.0305</v>
       </c>
       <c r="C6" s="5" t="inlineStr"/>
       <c r="D6" s="2" t="n"/>
@@ -1101,10 +1101,10 @@
     <col width="8" customWidth="1" min="17" max="17"/>
     <col width="8" customWidth="1" min="18" max="18"/>
     <col width="8" customWidth="1" min="19" max="19"/>
-    <col width="9" customWidth="1" min="20" max="20"/>
-    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="26" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
     <col width="9" customWidth="1" min="22" max="22"/>
-    <col width="23" customWidth="1" min="23" max="23"/>
+    <col width="28" customWidth="1" min="23" max="23"/>
     <col width="8" customWidth="1" min="24" max="24"/>
     <col width="8" customWidth="1" min="25" max="25"/>
     <col width="8" customWidth="1" min="26" max="26"/>
@@ -1390,7 +1390,7 @@
         <v>10.08</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>107.01</v>
+        <v>107.81</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>14.16</v>
@@ -1426,16 +1426,16 @@
         <v>9.75</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="T2" s="4" t="inlineStr">
         <is>
-          <t>近期无重大公告</t>
+          <t>公告偏风险(2个负面关键词, 0个异动/风险词)</t>
         </is>
       </c>
       <c r="U2" s="4" t="inlineStr">
         <is>
-          <t>无两融数据</t>
+          <t>融资余额上升2.9%</t>
         </is>
       </c>
       <c r="V2" s="4" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="W2" s="4" t="inlineStr">
         <is>
-          <t>近期无重大公告；无两融数据；近期未上龙虎榜</t>
+          <t>公告偏风险(2个负面关键词, 0个异动/风险词)；融资余额上升2.9%；近期未上龙虎榜</t>
         </is>
       </c>
       <c r="X2" s="4" t="n">
@@ -1553,7 +1553,7 @@
         <v>6.6</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>101.06</v>
+        <v>99.26000000000001</v>
       </c>
       <c r="H3" s="4" t="n">
         <v>15</v>
@@ -1589,16 +1589,16 @@
         <v>7.75</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>0</v>
+        <v>-1.8</v>
       </c>
       <c r="T3" s="4" t="inlineStr">
         <is>
-          <t>近期无重大公告</t>
+          <t>近期公告中性</t>
         </is>
       </c>
       <c r="U3" s="4" t="inlineStr">
         <is>
-          <t>无两融数据</t>
+          <t>融资余额下降-3.3%</t>
         </is>
       </c>
       <c r="V3" s="4" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="W3" s="4" t="inlineStr">
         <is>
-          <t>近期无重大公告；无两融数据；近期未上龙虎榜</t>
+          <t>近期公告中性；融资余额下降-3.3%；近期未上龙虎榜</t>
         </is>
       </c>
       <c r="X3" s="4" t="n">
@@ -1716,7 +1716,7 @@
         <v>6.67</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>98.97</v>
+        <v>99.17</v>
       </c>
       <c r="H4" s="4" t="n">
         <v>15</v>
@@ -1752,16 +1752,16 @@
         <v>7.88</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="T4" s="4" t="inlineStr">
         <is>
-          <t>近期无重大公告</t>
+          <t>近期公告中性</t>
         </is>
       </c>
       <c r="U4" s="4" t="inlineStr">
         <is>
-          <t>无两融数据</t>
+          <t>融资余额上升3.0%</t>
         </is>
       </c>
       <c r="V4" s="4" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="W4" s="4" t="inlineStr">
         <is>
-          <t>近期无重大公告；无两融数据；近期未上龙虎榜</t>
+          <t>近期公告中性；融资余额上升3.0%；近期未上龙虎榜</t>
         </is>
       </c>
       <c r="X4" s="4" t="n">
@@ -1919,22 +1919,22 @@
       </c>
       <c r="T5" s="4" t="inlineStr">
         <is>
-          <t>近期无重大公告</t>
+          <t>上下文数据超时</t>
         </is>
       </c>
       <c r="U5" s="4" t="inlineStr">
         <is>
-          <t>无两融数据</t>
+          <t>上下文数据超时</t>
         </is>
       </c>
       <c r="V5" s="4" t="inlineStr">
         <is>
-          <t>近期未上龙虎榜</t>
+          <t>上下文数据超时</t>
         </is>
       </c>
       <c r="W5" s="4" t="inlineStr">
         <is>
-          <t>近期无重大公告；无两融数据；近期未上龙虎榜</t>
+          <t>上下文数据超时</t>
         </is>
       </c>
       <c r="X5" s="4" t="n">
@@ -2042,7 +2042,7 @@
         <v>10</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>94.04000000000001</v>
+        <v>94.23999999999999</v>
       </c>
       <c r="H6" s="4" t="n">
         <v>12.8</v>
@@ -2078,16 +2078,16 @@
         <v>9.31</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="T6" s="4" t="inlineStr">
         <is>
-          <t>近期无重大公告</t>
+          <t>公告偏正面(4个积极关键词)</t>
         </is>
       </c>
       <c r="U6" s="4" t="inlineStr">
         <is>
-          <t>无两融数据</t>
+          <t>融资余额下降-12.6%</t>
         </is>
       </c>
       <c r="V6" s="4" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="W6" s="4" t="inlineStr">
         <is>
-          <t>近期无重大公告；无两融数据；近期未上龙虎榜</t>
+          <t>公告偏正面(4个积极关键词)；融资余额下降-12.6%；近期未上龙虎榜</t>
         </is>
       </c>
       <c r="X6" s="4" t="n">
@@ -2189,41 +2189,41 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>600058</t>
+          <t>601678</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>五矿发展</t>
+          <t>滨化股份</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="4" t="n">
-        <v>11.77</v>
+        <v>6.51</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>10</v>
+        <v>6.03</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>92.06999999999999</v>
+        <v>93.88</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>8.390000000000001</v>
+        <v>12.47</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.2231</v>
+        <v>1.6623</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>1.144329</v>
+        <v>1.126395</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>5.31</v>
+        <v>4.82</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>14.93</v>
+        <v>11.79</v>
       </c>
       <c r="N7" s="4" t="n">
         <v>8</v>
@@ -2232,25 +2232,25 @@
         <v>10</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>16.32</v>
+        <v>19.62</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>9.119999999999999</v>
+        <v>7.38</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T7" s="4" t="inlineStr">
         <is>
-          <t>近期无重大公告</t>
+          <t>近期公告中性</t>
         </is>
       </c>
       <c r="U7" s="4" t="inlineStr">
         <is>
-          <t>无两融数据</t>
+          <t>融资余额上升7.0%</t>
         </is>
       </c>
       <c r="V7" s="4" t="inlineStr">
@@ -2260,29 +2260,29 @@
       </c>
       <c r="W7" s="4" t="inlineStr">
         <is>
-          <t>近期无重大公告；无两融数据；近期未上龙虎榜</t>
+          <t>近期公告中性；融资余额上升7.0%；近期未上龙虎榜</t>
         </is>
       </c>
       <c r="X7" s="4" t="n">
-        <v>44.9</v>
+        <v>38.6</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>37.03</v>
+        <v>35.25</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>10.39</v>
+        <v>11.74</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AB7" s="4" t="n">
-        <v>0.115259</v>
+        <v>0.145687</v>
       </c>
       <c r="AC7" s="4" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.2625</v>
       </c>
       <c r="AD7" s="4" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.2625</v>
       </c>
       <c r="AE7" s="4" t="inlineStr">
         <is>
@@ -2293,56 +2293,56 @@
         <v>3</v>
       </c>
       <c r="AG7" s="4" t="n">
-        <v>10.95</v>
+        <v>6.05</v>
       </c>
       <c r="AH7" s="4" t="n">
-        <v>13.09</v>
+        <v>7.24</v>
       </c>
       <c r="AI7" s="4" t="n">
-        <v>13.95</v>
+        <v>7.69</v>
       </c>
       <c r="AJ7" s="4" t="n">
-        <v>10.95</v>
+        <v>6.08</v>
       </c>
       <c r="AK7" s="4" t="n">
         <v>1.6</v>
       </c>
       <c r="AL7" s="4" t="inlineStr">
         <is>
-          <t>3日短线计划；T+1看12.51/止损11.36；T+2看12.76/止损10.95；T+3看13.09/止损10.95</t>
+          <t>3日短线计划；T+1看6.92/止损6.28；T+2看7.06/止损6.11；T+3看7.24/止损6.08</t>
         </is>
       </c>
       <c r="AM7" s="4" t="n">
-        <v>11.36</v>
+        <v>6.28</v>
       </c>
       <c r="AN7" s="4" t="n">
-        <v>12.51</v>
+        <v>6.92</v>
       </c>
       <c r="AO7" s="4" t="inlineStr">
         <is>
-          <t>T+1：冲到12.51先减仓，跌破11.36止损；若高开低走不恋战</t>
+          <t>T+1：冲到6.92先减仓，跌破6.28止损；若高开低走不恋战</t>
         </is>
       </c>
       <c r="AP7" s="4" t="n">
-        <v>10.95</v>
+        <v>6.11</v>
       </c>
       <c r="AQ7" s="4" t="n">
-        <v>12.76</v>
+        <v>7.06</v>
       </c>
       <c r="AR7" s="4" t="inlineStr">
         <is>
-          <t>T+2：未突破12.76且量能转弱则减仓，跌破10.95退出</t>
+          <t>T+2：未突破7.06且量能转弱则减仓，跌破6.11退出</t>
         </is>
       </c>
       <c r="AS7" s="4" t="n">
-        <v>10.95</v>
+        <v>6.08</v>
       </c>
       <c r="AT7" s="4" t="n">
-        <v>13.09</v>
+        <v>7.24</v>
       </c>
       <c r="AU7" s="4" t="inlineStr">
         <is>
-          <t>T+3：到13.09分批止盈，跌破10.95或MA5失守退出</t>
+          <t>T+3：到7.24分批止盈，跌破6.08或MA5失守退出</t>
         </is>
       </c>
     </row>
@@ -2352,41 +2352,41 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>601678</t>
+          <t>600058</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>滨化股份</t>
+          <t>五矿发展</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="4" t="n">
-        <v>6.51</v>
+        <v>11.77</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>6.03</v>
+        <v>10</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>91.08</v>
+        <v>90.27</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>12.47</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>1.6623</v>
+        <v>-0.2231</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1.126395</v>
+        <v>1.144329</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>4.82</v>
+        <v>5.31</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>11.79</v>
+        <v>14.93</v>
       </c>
       <c r="N8" s="4" t="n">
         <v>8</v>
@@ -2395,25 +2395,25 @@
         <v>10</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>19.62</v>
+        <v>16.32</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>7.38</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0</v>
+        <v>-1.8</v>
       </c>
       <c r="T8" s="4" t="inlineStr">
         <is>
-          <t>近期无重大公告</t>
+          <t>近期公告中性</t>
         </is>
       </c>
       <c r="U8" s="4" t="inlineStr">
         <is>
-          <t>无两融数据</t>
+          <t>融资余额下降-1.9%</t>
         </is>
       </c>
       <c r="V8" s="4" t="inlineStr">
@@ -2423,29 +2423,29 @@
       </c>
       <c r="W8" s="4" t="inlineStr">
         <is>
-          <t>近期无重大公告；无两融数据；近期未上龙虎榜</t>
+          <t>近期公告中性；融资余额下降-1.9%；近期未上龙虎榜</t>
         </is>
       </c>
       <c r="X8" s="4" t="n">
-        <v>38.6</v>
+        <v>44.9</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>35.25</v>
+        <v>37.03</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>11.74</v>
+        <v>10.39</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AB8" s="4" t="n">
-        <v>0.145687</v>
+        <v>0.115259</v>
       </c>
       <c r="AC8" s="4" t="n">
-        <v>0.2625</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="AD8" s="4" t="n">
-        <v>0.2625</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="AE8" s="4" t="inlineStr">
         <is>
@@ -2456,56 +2456,56 @@
         <v>3</v>
       </c>
       <c r="AG8" s="4" t="n">
-        <v>6.05</v>
+        <v>10.95</v>
       </c>
       <c r="AH8" s="4" t="n">
-        <v>7.24</v>
+        <v>13.09</v>
       </c>
       <c r="AI8" s="4" t="n">
-        <v>7.69</v>
+        <v>13.95</v>
       </c>
       <c r="AJ8" s="4" t="n">
-        <v>6.08</v>
+        <v>10.95</v>
       </c>
       <c r="AK8" s="4" t="n">
         <v>1.6</v>
       </c>
       <c r="AL8" s="4" t="inlineStr">
         <is>
-          <t>3日短线计划；T+1看6.92/止损6.28；T+2看7.06/止损6.11；T+3看7.24/止损6.08</t>
+          <t>3日短线计划；T+1看12.51/止损11.36；T+2看12.76/止损10.95；T+3看13.09/止损10.95</t>
         </is>
       </c>
       <c r="AM8" s="4" t="n">
-        <v>6.28</v>
+        <v>11.36</v>
       </c>
       <c r="AN8" s="4" t="n">
-        <v>6.92</v>
+        <v>12.51</v>
       </c>
       <c r="AO8" s="4" t="inlineStr">
         <is>
-          <t>T+1：冲到6.92先减仓，跌破6.28止损；若高开低走不恋战</t>
+          <t>T+1：冲到12.51先减仓，跌破11.36止损；若高开低走不恋战</t>
         </is>
       </c>
       <c r="AP8" s="4" t="n">
-        <v>6.11</v>
+        <v>10.95</v>
       </c>
       <c r="AQ8" s="4" t="n">
-        <v>7.06</v>
+        <v>12.76</v>
       </c>
       <c r="AR8" s="4" t="inlineStr">
         <is>
-          <t>T+2：未突破7.06且量能转弱则减仓，跌破6.11退出</t>
+          <t>T+2：未突破12.76且量能转弱则减仓，跌破10.95退出</t>
         </is>
       </c>
       <c r="AS8" s="4" t="n">
-        <v>6.08</v>
+        <v>10.95</v>
       </c>
       <c r="AT8" s="4" t="n">
-        <v>7.24</v>
+        <v>13.09</v>
       </c>
       <c r="AU8" s="4" t="inlineStr">
         <is>
-          <t>T+3：到7.24分批止盈，跌破6.08或MA5失守退出</t>
+          <t>T+3：到13.09分批止盈，跌破10.95或MA5失守退出</t>
         </is>
       </c>
     </row>
@@ -2531,7 +2531,7 @@
         <v>4.27</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>90.8</v>
+        <v>90</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>14.97</v>
@@ -2567,16 +2567,16 @@
         <v>6</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="T9" s="4" t="inlineStr">
         <is>
-          <t>近期无重大公告</t>
+          <t>近期公告中性</t>
         </is>
       </c>
       <c r="U9" s="4" t="inlineStr">
         <is>
-          <t>无两融数据</t>
+          <t>融资余额下降-0.8%</t>
         </is>
       </c>
       <c r="V9" s="4" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="W9" s="4" t="inlineStr">
         <is>
-          <t>近期无重大公告；无两融数据；近期未上龙虎榜</t>
+          <t>近期公告中性；融资余额下降-0.8%；近期未上龙虎榜</t>
         </is>
       </c>
       <c r="X9" s="4" t="n">
@@ -2734,22 +2734,22 @@
       </c>
       <c r="T10" s="4" t="inlineStr">
         <is>
-          <t>近期无重大公告</t>
+          <t>上下文数据超时</t>
         </is>
       </c>
       <c r="U10" s="4" t="inlineStr">
         <is>
-          <t>无两融数据</t>
+          <t>上下文数据超时</t>
         </is>
       </c>
       <c r="V10" s="4" t="inlineStr">
         <is>
-          <t>近期未上龙虎榜</t>
+          <t>上下文数据超时</t>
         </is>
       </c>
       <c r="W10" s="4" t="inlineStr">
         <is>
-          <t>近期无重大公告；无两融数据；近期未上龙虎榜</t>
+          <t>上下文数据超时</t>
         </is>
       </c>
       <c r="X10" s="4" t="n">
@@ -2841,100 +2841,100 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>000100</t>
+          <t>000766</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>TCL科技</t>
+          <t>通化金马</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="4" t="n">
-        <v>5.34</v>
+        <v>26.61</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>89.7</v>
+        <v>89.66</v>
       </c>
       <c r="H11" s="4" t="n">
         <v>15</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>5.2684</v>
+        <v>3.4775</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1.125277</v>
+        <v>1.085259</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>5.84</v>
+        <v>10</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>9.449999999999999</v>
+        <v>7.43</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>10</v>
+        <v>5.25</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>4.53</v>
+        <v>14.67</v>
       </c>
       <c r="Q11" s="4" t="n">
         <v>20</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>9.880000000000001</v>
+        <v>9.31</v>
       </c>
       <c r="S11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="T11" s="4" t="inlineStr">
         <is>
-          <t>近期无重大公告</t>
+          <t>上下文数据超时</t>
         </is>
       </c>
       <c r="U11" s="4" t="inlineStr">
         <is>
-          <t>无两融数据</t>
+          <t>上下文数据超时</t>
         </is>
       </c>
       <c r="V11" s="4" t="inlineStr">
         <is>
-          <t>近期未上龙虎榜</t>
+          <t>上下文数据超时</t>
         </is>
       </c>
       <c r="W11" s="4" t="inlineStr">
         <is>
-          <t>近期无重大公告；无两融数据；近期未上龙虎榜</t>
+          <t>上下文数据超时</t>
         </is>
       </c>
       <c r="X11" s="4" t="n">
-        <v>33.9</v>
+        <v>29.9</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>38.9</v>
+        <v>32.92</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>13.38</v>
+        <v>11.1</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>1.46</v>
+        <v>3.78</v>
       </c>
       <c r="AB11" s="4" t="n">
-        <v>0.00655</v>
+        <v>0.100062</v>
       </c>
       <c r="AC11" s="4" t="n">
-        <v>0.0125</v>
+        <v>0.0688</v>
       </c>
       <c r="AD11" s="4" t="n">
-        <v>0.0125</v>
+        <v>0.0688</v>
       </c>
       <c r="AE11" s="4" t="inlineStr">
         <is>
@@ -2945,56 +2945,56 @@
         <v>2</v>
       </c>
       <c r="AG11" s="4" t="n">
-        <v>4.97</v>
+        <v>24.95</v>
       </c>
       <c r="AH11" s="4" t="n">
-        <v>5.94</v>
+        <v>29.26</v>
       </c>
       <c r="AI11" s="4" t="n">
-        <v>6.31</v>
+        <v>30.92</v>
       </c>
       <c r="AJ11" s="4" t="n">
-        <v>5.01</v>
+        <v>25.5</v>
       </c>
       <c r="AK11" s="4" t="n">
         <v>1.6</v>
       </c>
       <c r="AL11" s="4" t="inlineStr">
         <is>
-          <t>2日短线计划；T+1看5.68/止损5.15；T+2看5.79/止损4.98；T+3看5.94/止损5.01</t>
+          <t>2日短线计划；T+1看28.10/止损25.69；T+2看28.60/止损25.41；T+3看29.26/止损25.50</t>
         </is>
       </c>
       <c r="AM11" s="4" t="n">
-        <v>5.15</v>
+        <v>25.69</v>
       </c>
       <c r="AN11" s="4" t="n">
-        <v>5.68</v>
+        <v>28.1</v>
       </c>
       <c r="AO11" s="4" t="inlineStr">
         <is>
-          <t>T+1：冲到5.68先减仓，跌破5.15止损；若高开低走不恋战</t>
+          <t>T+1：冲到28.10先减仓，跌破25.69止损；若高开低走不恋战</t>
         </is>
       </c>
       <c r="AP11" s="4" t="n">
-        <v>4.98</v>
+        <v>25.41</v>
       </c>
       <c r="AQ11" s="4" t="n">
-        <v>5.79</v>
+        <v>28.6</v>
       </c>
       <c r="AR11" s="4" t="inlineStr">
         <is>
-          <t>T+2：未突破5.79且量能转弱则减仓，跌破4.98退出</t>
+          <t>T+2：未突破28.60且量能转弱则减仓，跌破25.41退出</t>
         </is>
       </c>
       <c r="AS11" s="4" t="n">
-        <v>5.01</v>
+        <v>25.5</v>
       </c>
       <c r="AT11" s="4" t="n">
-        <v>5.94</v>
+        <v>29.26</v>
       </c>
       <c r="AU11" s="4" t="inlineStr">
         <is>
-          <t>T+3：到5.94分批止盈，跌破5.01或MA5失守退出</t>
+          <t>T+3：到29.26分批止盈，跌破25.50或MA5失守退出</t>
         </is>
       </c>
     </row>
@@ -3004,160 +3004,160 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>000766</t>
+          <t>000783</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>通化金马</t>
+          <t>长江证券</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="4" t="n">
-        <v>26.61</v>
+        <v>10.15</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>10</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>89.66</v>
+        <v>89.59</v>
       </c>
       <c r="H12" s="4" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>0.2668</v>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>1.256344</v>
+      </c>
+      <c r="L12" s="4" t="n">
+        <v>8.48</v>
+      </c>
+      <c r="M12" s="4" t="n">
         <v>15</v>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="J12" s="4" t="n">
-        <v>3.4775</v>
-      </c>
-      <c r="K12" s="4" t="n">
-        <v>1.085259</v>
-      </c>
-      <c r="L12" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="M12" s="4" t="n">
-        <v>7.43</v>
       </c>
       <c r="N12" s="4" t="n">
         <v>8</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>5.25</v>
+        <v>10</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>14.67</v>
+        <v>18.1</v>
       </c>
       <c r="Q12" s="4" t="n">
         <v>20</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>9.31</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="S12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="T12" s="4" t="inlineStr">
         <is>
-          <t>近期无重大公告</t>
+          <t>上下文数据超时</t>
         </is>
       </c>
       <c r="U12" s="4" t="inlineStr">
         <is>
-          <t>无两融数据</t>
+          <t>上下文数据超时</t>
         </is>
       </c>
       <c r="V12" s="4" t="inlineStr">
         <is>
-          <t>近期未上龙虎榜</t>
+          <t>上下文数据超时</t>
         </is>
       </c>
       <c r="W12" s="4" t="inlineStr">
         <is>
-          <t>近期无重大公告；无两融数据；近期未上龙虎榜</t>
+          <t>上下文数据超时</t>
         </is>
       </c>
       <c r="X12" s="4" t="n">
-        <v>29.9</v>
+        <v>53.6</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>32.92</v>
+        <v>48.53</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>11.1</v>
+        <v>4.93</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>3.78</v>
+        <v>2.12</v>
       </c>
       <c r="AB12" s="4" t="n">
-        <v>0.100062</v>
+        <v>0.131632</v>
       </c>
       <c r="AC12" s="4" t="n">
-        <v>0.0688</v>
+        <v>0.1125</v>
       </c>
       <c r="AD12" s="4" t="n">
-        <v>0.0688</v>
+        <v>0.1125</v>
       </c>
       <c r="AE12" s="4" t="inlineStr">
         <is>
-          <t>🟡 首日上涨，可关注</t>
+          <t>🟠 远离均线，不宜追高</t>
         </is>
       </c>
       <c r="AF12" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG12" s="4" t="n">
-        <v>24.95</v>
+        <v>9.44</v>
       </c>
       <c r="AH12" s="4" t="n">
-        <v>29.26</v>
+        <v>11.29</v>
       </c>
       <c r="AI12" s="4" t="n">
-        <v>30.92</v>
+        <v>12</v>
       </c>
       <c r="AJ12" s="4" t="n">
-        <v>25.5</v>
+        <v>9.59</v>
       </c>
       <c r="AK12" s="4" t="n">
         <v>1.6</v>
       </c>
       <c r="AL12" s="4" t="inlineStr">
         <is>
-          <t>2日短线计划；T+1看28.10/止损25.69；T+2看28.60/止损25.41；T+3看29.26/止损25.50</t>
+          <t>1日短线计划；T+1看10.79/止损9.79；T+2看11.00/止损9.54；T+3看11.29/止损9.59</t>
         </is>
       </c>
       <c r="AM12" s="4" t="n">
-        <v>25.69</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="AN12" s="4" t="n">
-        <v>28.1</v>
+        <v>10.79</v>
       </c>
       <c r="AO12" s="4" t="inlineStr">
         <is>
-          <t>T+1：冲到28.10先减仓，跌破25.69止损；若高开低走不恋战</t>
+          <t>T+1：冲到10.79先减仓，跌破9.79止损；若高开低走不恋战</t>
         </is>
       </c>
       <c r="AP12" s="4" t="n">
-        <v>25.41</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="AQ12" s="4" t="n">
-        <v>28.6</v>
+        <v>11</v>
       </c>
       <c r="AR12" s="4" t="inlineStr">
         <is>
-          <t>T+2：未突破28.60且量能转弱则减仓，跌破25.41退出</t>
+          <t>T+2：未突破11.00且量能转弱则减仓，跌破9.54退出</t>
         </is>
       </c>
       <c r="AS12" s="4" t="n">
-        <v>25.5</v>
+        <v>9.59</v>
       </c>
       <c r="AT12" s="4" t="n">
-        <v>29.26</v>
+        <v>11.29</v>
       </c>
       <c r="AU12" s="4" t="inlineStr">
         <is>
-          <t>T+3：到29.26分批止盈，跌破25.50或MA5失守退出</t>
+          <t>T+3：到11.29分批止盈，跌破9.59或MA5失守退出</t>
         </is>
       </c>
     </row>
@@ -3167,38 +3167,38 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>000783</t>
+          <t>000021</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>长江证券</t>
+          <t>深科技</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="4" t="n">
-        <v>10.15</v>
+        <v>53.2</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>9.970000000000001</v>
+        <v>5.83</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>89.59</v>
+        <v>89.33</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>5.13</v>
+        <v>13.1</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.2668</v>
+        <v>7.3979</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>1.256344</v>
+        <v>1.293082</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>8.48</v>
+        <v>4.91</v>
       </c>
       <c r="M13" s="4" t="n">
         <v>15</v>
@@ -3210,57 +3210,57 @@
         <v>10</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>18.1</v>
+        <v>20.2</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>8.880000000000001</v>
+        <v>7.12</v>
       </c>
       <c r="S13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="T13" s="4" t="inlineStr">
         <is>
-          <t>近期无重大公告</t>
+          <t>上下文数据超时</t>
         </is>
       </c>
       <c r="U13" s="4" t="inlineStr">
         <is>
-          <t>无两融数据</t>
+          <t>上下文数据超时</t>
         </is>
       </c>
       <c r="V13" s="4" t="inlineStr">
         <is>
-          <t>近期未上龙虎榜</t>
+          <t>上下文数据超时</t>
         </is>
       </c>
       <c r="W13" s="4" t="inlineStr">
         <is>
-          <t>近期无重大公告；无两融数据；近期未上龙虎榜</t>
+          <t>上下文数据超时</t>
         </is>
       </c>
       <c r="X13" s="4" t="n">
-        <v>53.6</v>
+        <v>54.8</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>48.53</v>
+        <v>46.5</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>4.93</v>
+        <v>4.28</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>2.12</v>
+        <v>1.23</v>
       </c>
       <c r="AB13" s="4" t="n">
-        <v>0.131632</v>
+        <v>0.151</v>
       </c>
       <c r="AC13" s="4" t="n">
-        <v>0.1125</v>
+        <v>0.2875</v>
       </c>
       <c r="AD13" s="4" t="n">
-        <v>0.1125</v>
+        <v>0.2875</v>
       </c>
       <c r="AE13" s="4" t="inlineStr">
         <is>
@@ -3271,56 +3271,56 @@
         <v>1</v>
       </c>
       <c r="AG13" s="4" t="n">
-        <v>9.44</v>
+        <v>49.48</v>
       </c>
       <c r="AH13" s="4" t="n">
-        <v>11.29</v>
+        <v>59.16</v>
       </c>
       <c r="AI13" s="4" t="n">
-        <v>12</v>
+        <v>62.99</v>
       </c>
       <c r="AJ13" s="4" t="n">
-        <v>9.59</v>
+        <v>49.48</v>
       </c>
       <c r="AK13" s="4" t="n">
         <v>1.6</v>
       </c>
       <c r="AL13" s="4" t="inlineStr">
         <is>
-          <t>1日短线计划；T+1看10.79/止损9.79；T+2看11.00/止损9.54；T+3看11.29/止损9.59</t>
+          <t>1日短线计划；T+1看56.55/止损51.34；T+2看57.67/止损49.48；T+3看59.16/止损49.48</t>
         </is>
       </c>
       <c r="AM13" s="4" t="n">
-        <v>9.789999999999999</v>
+        <v>51.34</v>
       </c>
       <c r="AN13" s="4" t="n">
-        <v>10.79</v>
+        <v>56.55</v>
       </c>
       <c r="AO13" s="4" t="inlineStr">
         <is>
-          <t>T+1：冲到10.79先减仓，跌破9.79止损；若高开低走不恋战</t>
+          <t>T+1：冲到56.55先减仓，跌破51.34止损；若高开低走不恋战</t>
         </is>
       </c>
       <c r="AP13" s="4" t="n">
-        <v>9.539999999999999</v>
+        <v>49.48</v>
       </c>
       <c r="AQ13" s="4" t="n">
-        <v>11</v>
+        <v>57.67</v>
       </c>
       <c r="AR13" s="4" t="inlineStr">
         <is>
-          <t>T+2：未突破11.00且量能转弱则减仓，跌破9.54退出</t>
+          <t>T+2：未突破57.67且量能转弱则减仓，跌破49.48退出</t>
         </is>
       </c>
       <c r="AS13" s="4" t="n">
-        <v>9.59</v>
+        <v>49.48</v>
       </c>
       <c r="AT13" s="4" t="n">
-        <v>11.29</v>
+        <v>59.16</v>
       </c>
       <c r="AU13" s="4" t="inlineStr">
         <is>
-          <t>T+3：到11.29分批止盈，跌破9.59或MA5失守退出</t>
+          <t>T+3：到59.16分批止盈，跌破49.48或MA5失守退出</t>
         </is>
       </c>
     </row>
@@ -3330,38 +3330,38 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>600141</t>
+          <t>601162</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>兴发集团</t>
+          <t>天风证券</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="4" t="n">
-        <v>47.48</v>
+        <v>3.59</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>10.01</v>
+        <v>4.36</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>89.37</v>
+        <v>89.31999999999999</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>11</v>
+        <v>8.52</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>10.9779</v>
+        <v>-3.0071</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1.367906</v>
+        <v>1.091185</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>6.33</v>
+        <v>5.52</v>
       </c>
       <c r="M14" s="4" t="n">
         <v>15</v>
@@ -3370,28 +3370,28 @@
         <v>8</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>10</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>13.54</v>
+        <v>20.09</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>9.5</v>
+        <v>6.12</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="T14" s="4" t="inlineStr">
         <is>
-          <t>近期无重大公告</t>
+          <t>近期公告中性</t>
         </is>
       </c>
       <c r="U14" s="4" t="inlineStr">
         <is>
-          <t>无两融数据</t>
+          <t>融资余额上升1.2%</t>
         </is>
       </c>
       <c r="V14" s="4" t="inlineStr">
@@ -3401,89 +3401,89 @@
       </c>
       <c r="W14" s="4" t="inlineStr">
         <is>
-          <t>近期无重大公告；无两融数据；近期未上龙虎榜</t>
+          <t>近期公告中性；融资余额上升1.2%；近期未上龙虎榜</t>
         </is>
       </c>
       <c r="X14" s="4" t="n">
-        <v>64.3</v>
+        <v>46.9</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>51.55</v>
+        <v>37.32</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>4.6</v>
+        <v>9.65</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>1.58</v>
+        <v>1.38</v>
       </c>
       <c r="AB14" s="4" t="n">
-        <v>0.08958099999999999</v>
+        <v>0.150034</v>
       </c>
       <c r="AC14" s="4" t="n">
-        <v>0.05</v>
+        <v>0.3875</v>
       </c>
       <c r="AD14" s="4" t="n">
-        <v>0.05</v>
+        <v>0.3875</v>
       </c>
       <c r="AE14" s="4" t="inlineStr">
         <is>
-          <t>🟠 远离均线，不宜追高</t>
+          <t>🟡 首日上涨，可关注</t>
         </is>
       </c>
       <c r="AF14" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AG14" s="4" t="n">
-        <v>44.16</v>
+        <v>3.34</v>
       </c>
       <c r="AH14" s="4" t="n">
-        <v>52.8</v>
+        <v>3.99</v>
       </c>
       <c r="AI14" s="4" t="n">
-        <v>56.87</v>
+        <v>4.24</v>
       </c>
       <c r="AJ14" s="4" t="n">
-        <v>44.16</v>
+        <v>3.4</v>
       </c>
       <c r="AK14" s="4" t="n">
         <v>1.6</v>
       </c>
       <c r="AL14" s="4" t="inlineStr">
         <is>
-          <t>1日短线计划；T+1看50.47/止损45.82；T+2看51.47/止损44.16；T+3看52.80/止损44.16</t>
+          <t>3日短线计划；T+1看3.82/止损3.46；T+2看3.89/止损3.39；T+3看3.99/止损3.40</t>
         </is>
       </c>
       <c r="AM14" s="4" t="n">
-        <v>45.82</v>
+        <v>3.46</v>
       </c>
       <c r="AN14" s="4" t="n">
-        <v>50.47</v>
+        <v>3.82</v>
       </c>
       <c r="AO14" s="4" t="inlineStr">
         <is>
-          <t>T+1：冲到50.47先减仓，跌破45.82止损；若高开低走不恋战</t>
+          <t>T+1：冲到3.82先减仓，跌破3.46止损；若高开低走不恋战</t>
         </is>
       </c>
       <c r="AP14" s="4" t="n">
-        <v>44.16</v>
+        <v>3.39</v>
       </c>
       <c r="AQ14" s="4" t="n">
-        <v>51.47</v>
+        <v>3.89</v>
       </c>
       <c r="AR14" s="4" t="inlineStr">
         <is>
-          <t>T+2：未突破51.47且量能转弱则减仓，跌破44.16退出</t>
+          <t>T+2：未突破3.89且量能转弱则减仓，跌破3.39退出</t>
         </is>
       </c>
       <c r="AS14" s="4" t="n">
-        <v>44.16</v>
+        <v>3.4</v>
       </c>
       <c r="AT14" s="4" t="n">
-        <v>52.8</v>
+        <v>3.99</v>
       </c>
       <c r="AU14" s="4" t="inlineStr">
         <is>
-          <t>T+3：到52.80分批止盈，跌破44.16或MA5失守退出</t>
+          <t>T+3：到3.99分批止盈，跌破3.40或MA5失守退出</t>
         </is>
       </c>
     </row>
@@ -3493,38 +3493,38 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>000021</t>
+          <t>600141</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>深科技</t>
+          <t>兴发集团</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr"/>
       <c r="E15" s="4" t="n">
-        <v>53.2</v>
+        <v>47.48</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>5.83</v>
+        <v>10.01</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>89.33</v>
+        <v>88.77</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>13.1</v>
+        <v>11</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>7.3979</v>
+        <v>10.9779</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1.293082</v>
+        <v>1.367906</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>4.91</v>
+        <v>6.33</v>
       </c>
       <c r="M15" s="4" t="n">
         <v>15</v>
@@ -3536,25 +3536,25 @@
         <v>10</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>20.2</v>
+        <v>13.54</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>7.12</v>
+        <v>9.5</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="T15" s="4" t="inlineStr">
         <is>
-          <t>近期无重大公告</t>
+          <t>公告偏风险(0个负面关键词, 1个异动/风险词)</t>
         </is>
       </c>
       <c r="U15" s="4" t="inlineStr">
         <is>
-          <t>无两融数据</t>
+          <t>融资余额上升3.7%</t>
         </is>
       </c>
       <c r="V15" s="4" t="inlineStr">
@@ -3564,29 +3564,29 @@
       </c>
       <c r="W15" s="4" t="inlineStr">
         <is>
-          <t>近期无重大公告；无两融数据；近期未上龙虎榜</t>
+          <t>公告偏风险(0个负面关键词, 1个异动/风险词)；融资余额上升3.7%；近期未上龙虎榜</t>
         </is>
       </c>
       <c r="X15" s="4" t="n">
-        <v>54.8</v>
+        <v>64.3</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>46.5</v>
+        <v>51.55</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>4.28</v>
+        <v>4.6</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>1.23</v>
+        <v>1.58</v>
       </c>
       <c r="AB15" s="4" t="n">
-        <v>0.151</v>
+        <v>0.08958099999999999</v>
       </c>
       <c r="AC15" s="4" t="n">
-        <v>0.2875</v>
+        <v>0.05</v>
       </c>
       <c r="AD15" s="4" t="n">
-        <v>0.2875</v>
+        <v>0.05</v>
       </c>
       <c r="AE15" s="4" t="inlineStr">
         <is>
@@ -3597,56 +3597,56 @@
         <v>1</v>
       </c>
       <c r="AG15" s="4" t="n">
-        <v>49.48</v>
+        <v>44.16</v>
       </c>
       <c r="AH15" s="4" t="n">
-        <v>59.16</v>
+        <v>52.8</v>
       </c>
       <c r="AI15" s="4" t="n">
-        <v>62.99</v>
+        <v>56.87</v>
       </c>
       <c r="AJ15" s="4" t="n">
-        <v>49.48</v>
+        <v>44.16</v>
       </c>
       <c r="AK15" s="4" t="n">
         <v>1.6</v>
       </c>
       <c r="AL15" s="4" t="inlineStr">
         <is>
-          <t>1日短线计划；T+1看56.55/止损51.34；T+2看57.67/止损49.48；T+3看59.16/止损49.48</t>
+          <t>1日短线计划；T+1看50.47/止损45.82；T+2看51.47/止损44.16；T+3看52.80/止损44.16</t>
         </is>
       </c>
       <c r="AM15" s="4" t="n">
-        <v>51.34</v>
+        <v>45.82</v>
       </c>
       <c r="AN15" s="4" t="n">
-        <v>56.55</v>
+        <v>50.47</v>
       </c>
       <c r="AO15" s="4" t="inlineStr">
         <is>
-          <t>T+1：冲到56.55先减仓，跌破51.34止损；若高开低走不恋战</t>
+          <t>T+1：冲到50.47先减仓，跌破45.82止损；若高开低走不恋战</t>
         </is>
       </c>
       <c r="AP15" s="4" t="n">
-        <v>49.48</v>
+        <v>44.16</v>
       </c>
       <c r="AQ15" s="4" t="n">
-        <v>57.67</v>
+        <v>51.47</v>
       </c>
       <c r="AR15" s="4" t="inlineStr">
         <is>
-          <t>T+2：未突破57.67且量能转弱则减仓，跌破49.48退出</t>
+          <t>T+2：未突破51.47且量能转弱则减仓，跌破44.16退出</t>
         </is>
       </c>
       <c r="AS15" s="4" t="n">
-        <v>49.48</v>
+        <v>44.16</v>
       </c>
       <c r="AT15" s="4" t="n">
-        <v>59.16</v>
+        <v>52.8</v>
       </c>
       <c r="AU15" s="4" t="inlineStr">
         <is>
-          <t>T+3：到59.16分批止盈，跌破49.48或MA5失守退出</t>
+          <t>T+3：到52.80分批止盈，跌破44.16或MA5失守退出</t>
         </is>
       </c>
     </row>
@@ -3656,68 +3656,68 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>601162</t>
+          <t>000100</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>天风证券</t>
+          <t>TCL科技</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="4" t="n">
-        <v>3.59</v>
+        <v>5.34</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>4.36</v>
+        <v>10.1</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>89.12</v>
+        <v>88.5</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>8.52</v>
+        <v>15</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-3.0071</v>
+        <v>5.2684</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1.091185</v>
+        <v>1.125277</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>5.52</v>
+        <v>5.84</v>
       </c>
       <c r="M16" s="4" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="N16" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="N16" s="4" t="n">
-        <v>8</v>
-      </c>
       <c r="O16" s="4" t="n">
-        <v>8.869999999999999</v>
+        <v>10</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>20.09</v>
+        <v>4.53</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>6.12</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0</v>
+        <v>-1.2</v>
       </c>
       <c r="T16" s="4" t="inlineStr">
         <is>
-          <t>近期无重大公告</t>
+          <t>公告偏风险(5个负面关键词, 0个异动/风险词)</t>
         </is>
       </c>
       <c r="U16" s="4" t="inlineStr">
         <is>
-          <t>无两融数据</t>
+          <t>融资余额上升2.5%</t>
         </is>
       </c>
       <c r="V16" s="4" t="inlineStr">
@@ -3727,29 +3727,29 @@
       </c>
       <c r="W16" s="4" t="inlineStr">
         <is>
-          <t>近期无重大公告；无两融数据；近期未上龙虎榜</t>
+          <t>公告偏风险(5个负面关键词, 0个异动/风险词)；融资余额上升2.5%；近期未上龙虎榜</t>
         </is>
       </c>
       <c r="X16" s="4" t="n">
-        <v>46.9</v>
+        <v>33.9</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>37.32</v>
+        <v>38.9</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>9.65</v>
+        <v>13.38</v>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="AB16" s="4" t="n">
-        <v>0.150034</v>
+        <v>0.00655</v>
       </c>
       <c r="AC16" s="4" t="n">
-        <v>0.3875</v>
+        <v>0.0125</v>
       </c>
       <c r="AD16" s="4" t="n">
-        <v>0.3875</v>
+        <v>0.0125</v>
       </c>
       <c r="AE16" s="4" t="inlineStr">
         <is>
@@ -3757,59 +3757,59 @@
         </is>
       </c>
       <c r="AF16" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG16" s="4" t="n">
-        <v>3.34</v>
+        <v>4.97</v>
       </c>
       <c r="AH16" s="4" t="n">
-        <v>3.99</v>
+        <v>5.94</v>
       </c>
       <c r="AI16" s="4" t="n">
-        <v>4.24</v>
+        <v>6.31</v>
       </c>
       <c r="AJ16" s="4" t="n">
-        <v>3.4</v>
+        <v>5.01</v>
       </c>
       <c r="AK16" s="4" t="n">
         <v>1.6</v>
       </c>
       <c r="AL16" s="4" t="inlineStr">
         <is>
-          <t>3日短线计划；T+1看3.82/止损3.46；T+2看3.89/止损3.39；T+3看3.99/止损3.40</t>
+          <t>2日短线计划；T+1看5.68/止损5.15；T+2看5.79/止损4.98；T+3看5.94/止损5.01</t>
         </is>
       </c>
       <c r="AM16" s="4" t="n">
-        <v>3.46</v>
+        <v>5.15</v>
       </c>
       <c r="AN16" s="4" t="n">
-        <v>3.82</v>
+        <v>5.68</v>
       </c>
       <c r="AO16" s="4" t="inlineStr">
         <is>
-          <t>T+1：冲到3.82先减仓，跌破3.46止损；若高开低走不恋战</t>
+          <t>T+1：冲到5.68先减仓，跌破5.15止损；若高开低走不恋战</t>
         </is>
       </c>
       <c r="AP16" s="4" t="n">
-        <v>3.39</v>
+        <v>4.98</v>
       </c>
       <c r="AQ16" s="4" t="n">
-        <v>3.89</v>
+        <v>5.79</v>
       </c>
       <c r="AR16" s="4" t="inlineStr">
         <is>
-          <t>T+2：未突破3.89且量能转弱则减仓，跌破3.39退出</t>
+          <t>T+2：未突破5.79且量能转弱则减仓，跌破4.98退出</t>
         </is>
       </c>
       <c r="AS16" s="4" t="n">
-        <v>3.4</v>
+        <v>5.01</v>
       </c>
       <c r="AT16" s="4" t="n">
-        <v>3.99</v>
+        <v>5.94</v>
       </c>
       <c r="AU16" s="4" t="inlineStr">
         <is>
-          <t>T+3：到3.99分批止盈，跌破3.40或MA5失守退出</t>
+          <t>T+3：到5.94分批止盈，跌破5.01或MA5失守退出</t>
         </is>
       </c>
     </row>
@@ -3875,22 +3875,22 @@
       </c>
       <c r="T17" s="4" t="inlineStr">
         <is>
-          <t>近期无重大公告</t>
+          <t>上下文数据超时</t>
         </is>
       </c>
       <c r="U17" s="4" t="inlineStr">
         <is>
-          <t>无两融数据</t>
+          <t>上下文数据超时</t>
         </is>
       </c>
       <c r="V17" s="4" t="inlineStr">
         <is>
-          <t>近期未上龙虎榜</t>
+          <t>上下文数据超时</t>
         </is>
       </c>
       <c r="W17" s="4" t="inlineStr">
         <is>
-          <t>近期无重大公告；无两融数据；近期未上龙虎榜</t>
+          <t>上下文数据超时</t>
         </is>
       </c>
       <c r="X17" s="4" t="n">
@@ -3982,41 +3982,41 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>600400</t>
+          <t>000066</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>红豆股份</t>
+          <t>中国长城</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="4" t="n">
-        <v>3.35</v>
+        <v>20.47</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>6.69</v>
+        <v>7.74</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>86.45999999999999</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>4.5</v>
+        <v>6.53</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-3.0267</v>
+        <v>-7.6535</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.181449</v>
+        <v>1.170818</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>5.75</v>
+        <v>6.12</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>14.37</v>
+        <v>13.61</v>
       </c>
       <c r="N18" s="4" t="n">
         <v>8</v>
@@ -4025,57 +4025,57 @@
         <v>10</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>24.83</v>
+        <v>22.13</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>15</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>8</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="S18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="T18" s="4" t="inlineStr">
         <is>
-          <t>近期无重大公告</t>
+          <t>上下文数据超时</t>
         </is>
       </c>
       <c r="U18" s="4" t="inlineStr">
         <is>
-          <t>无两融数据</t>
+          <t>上下文数据超时</t>
         </is>
       </c>
       <c r="V18" s="4" t="inlineStr">
         <is>
-          <t>近期未上龙虎榜</t>
+          <t>上下文数据超时</t>
         </is>
       </c>
       <c r="W18" s="4" t="inlineStr">
         <is>
-          <t>近期无重大公告；无两融数据；近期未上龙虎榜</t>
+          <t>上下文数据超时</t>
         </is>
       </c>
       <c r="X18" s="4" t="n">
-        <v>43.7</v>
+        <v>42.2</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>39.95</v>
+        <v>38.71</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>7.91</v>
+        <v>8.49</v>
       </c>
       <c r="AA18" s="4" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AB18" s="4" t="n">
-        <v>0.193786</v>
+        <v>0.168841</v>
       </c>
       <c r="AC18" s="4" t="n">
-        <v>0.2</v>
+        <v>0.1625</v>
       </c>
       <c r="AD18" s="4" t="n">
-        <v>0.2</v>
+        <v>0.1625</v>
       </c>
       <c r="AE18" s="4" t="inlineStr">
         <is>
@@ -4086,56 +4086,56 @@
         <v>1</v>
       </c>
       <c r="AG18" s="4" t="n">
-        <v>3.12</v>
+        <v>19.04</v>
       </c>
       <c r="AH18" s="4" t="n">
-        <v>3.73</v>
+        <v>22.76</v>
       </c>
       <c r="AI18" s="4" t="n">
-        <v>3.96</v>
+        <v>24.2</v>
       </c>
       <c r="AJ18" s="4" t="n">
-        <v>3.12</v>
+        <v>19.14</v>
       </c>
       <c r="AK18" s="4" t="n">
         <v>1.6</v>
       </c>
       <c r="AL18" s="4" t="inlineStr">
         <is>
-          <t>1日短线计划；T+1看3.56/止损3.23；T+2看3.63/止损3.12；T+3看3.73/止损3.12</t>
+          <t>1日短线计划；T+1看21.76/止损19.75；T+2看22.19/止损19.04；T+3看22.76/止损19.14</t>
         </is>
       </c>
       <c r="AM18" s="4" t="n">
-        <v>3.23</v>
+        <v>19.75</v>
       </c>
       <c r="AN18" s="4" t="n">
-        <v>3.56</v>
+        <v>21.76</v>
       </c>
       <c r="AO18" s="4" t="inlineStr">
         <is>
-          <t>T+1：冲到3.56先减仓，跌破3.23止损；若高开低走不恋战</t>
+          <t>T+1：冲到21.76先减仓，跌破19.75止损；若高开低走不恋战</t>
         </is>
       </c>
       <c r="AP18" s="4" t="n">
-        <v>3.12</v>
+        <v>19.04</v>
       </c>
       <c r="AQ18" s="4" t="n">
-        <v>3.63</v>
+        <v>22.19</v>
       </c>
       <c r="AR18" s="4" t="inlineStr">
         <is>
-          <t>T+2：未突破3.63且量能转弱则减仓，跌破3.12退出</t>
+          <t>T+2：未突破22.19且量能转弱则减仓，跌破19.04退出</t>
         </is>
       </c>
       <c r="AS18" s="4" t="n">
-        <v>3.12</v>
+        <v>19.14</v>
       </c>
       <c r="AT18" s="4" t="n">
-        <v>3.73</v>
+        <v>22.76</v>
       </c>
       <c r="AU18" s="4" t="inlineStr">
         <is>
-          <t>T+3：到3.73分批止盈，跌破3.12或MA5失守退出</t>
+          <t>T+3：到22.76分批止盈，跌破19.14或MA5失守退出</t>
         </is>
       </c>
     </row>
@@ -4145,41 +4145,41 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>000066</t>
+          <t>600400</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>中国长城</t>
+          <t>红豆股份</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr"/>
       <c r="E19" s="4" t="n">
-        <v>20.47</v>
+        <v>3.35</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>7.74</v>
+        <v>6.69</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>85.76000000000001</v>
+        <v>84.66</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>6.53</v>
+        <v>4.5</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-7.6535</v>
+        <v>-3.0267</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.170818</v>
+        <v>1.181449</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>6.12</v>
+        <v>5.75</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>13.61</v>
+        <v>14.37</v>
       </c>
       <c r="N19" s="4" t="n">
         <v>8</v>
@@ -4188,25 +4188,25 @@
         <v>10</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>22.13</v>
+        <v>24.83</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>15</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>8.380000000000001</v>
+        <v>8</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0</v>
+        <v>-1.8</v>
       </c>
       <c r="T19" s="4" t="inlineStr">
         <is>
-          <t>近期无重大公告</t>
+          <t>公告偏风险(2个负面关键词, 1个异动/风险词)</t>
         </is>
       </c>
       <c r="U19" s="4" t="inlineStr">
         <is>
-          <t>无两融数据</t>
+          <t>融资余额上升16.3%</t>
         </is>
       </c>
       <c r="V19" s="4" t="inlineStr">
@@ -4216,29 +4216,29 @@
       </c>
       <c r="W19" s="4" t="inlineStr">
         <is>
-          <t>近期无重大公告；无两融数据；近期未上龙虎榜</t>
+          <t>公告偏风险(2个负面关键词, 1个异动/风险词)；融资余额上升16.3%；近期未上龙虎榜</t>
         </is>
       </c>
       <c r="X19" s="4" t="n">
-        <v>42.2</v>
+        <v>43.7</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>38.71</v>
+        <v>39.95</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>8.49</v>
+        <v>7.91</v>
       </c>
       <c r="AA19" s="4" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AB19" s="4" t="n">
-        <v>0.168841</v>
+        <v>0.193786</v>
       </c>
       <c r="AC19" s="4" t="n">
-        <v>0.1625</v>
+        <v>0.2</v>
       </c>
       <c r="AD19" s="4" t="n">
-        <v>0.1625</v>
+        <v>0.2</v>
       </c>
       <c r="AE19" s="4" t="inlineStr">
         <is>
@@ -4249,56 +4249,56 @@
         <v>1</v>
       </c>
       <c r="AG19" s="4" t="n">
-        <v>19.04</v>
+        <v>3.12</v>
       </c>
       <c r="AH19" s="4" t="n">
-        <v>22.76</v>
+        <v>3.73</v>
       </c>
       <c r="AI19" s="4" t="n">
-        <v>24.2</v>
+        <v>3.96</v>
       </c>
       <c r="AJ19" s="4" t="n">
-        <v>19.14</v>
+        <v>3.12</v>
       </c>
       <c r="AK19" s="4" t="n">
         <v>1.6</v>
       </c>
       <c r="AL19" s="4" t="inlineStr">
         <is>
-          <t>1日短线计划；T+1看21.76/止损19.75；T+2看22.19/止损19.04；T+3看22.76/止损19.14</t>
+          <t>1日短线计划；T+1看3.56/止损3.23；T+2看3.63/止损3.12；T+3看3.73/止损3.12</t>
         </is>
       </c>
       <c r="AM19" s="4" t="n">
-        <v>19.75</v>
+        <v>3.23</v>
       </c>
       <c r="AN19" s="4" t="n">
-        <v>21.76</v>
+        <v>3.56</v>
       </c>
       <c r="AO19" s="4" t="inlineStr">
         <is>
-          <t>T+1：冲到21.76先减仓，跌破19.75止损；若高开低走不恋战</t>
+          <t>T+1：冲到3.56先减仓，跌破3.23止损；若高开低走不恋战</t>
         </is>
       </c>
       <c r="AP19" s="4" t="n">
-        <v>19.04</v>
+        <v>3.12</v>
       </c>
       <c r="AQ19" s="4" t="n">
-        <v>22.19</v>
+        <v>3.63</v>
       </c>
       <c r="AR19" s="4" t="inlineStr">
         <is>
-          <t>T+2：未突破22.19且量能转弱则减仓，跌破19.04退出</t>
+          <t>T+2：未突破3.63且量能转弱则减仓，跌破3.12退出</t>
         </is>
       </c>
       <c r="AS19" s="4" t="n">
-        <v>19.14</v>
+        <v>3.12</v>
       </c>
       <c r="AT19" s="4" t="n">
-        <v>22.76</v>
+        <v>3.73</v>
       </c>
       <c r="AU19" s="4" t="inlineStr">
         <is>
-          <t>T+3：到22.76分批止盈，跌破19.14或MA5失守退出</t>
+          <t>T+3：到3.73分批止盈，跌破3.12或MA5失守退出</t>
         </is>
       </c>
     </row>
@@ -4324,7 +4324,7 @@
         <v>3.91</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>85.58</v>
+        <v>83.78</v>
       </c>
       <c r="H20" s="4" t="n">
         <v>12.22</v>
@@ -4360,16 +4360,16 @@
         <v>5.62</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0</v>
+        <v>-1.8</v>
       </c>
       <c r="T20" s="4" t="inlineStr">
         <is>
-          <t>近期无重大公告</t>
+          <t>近期公告中性</t>
         </is>
       </c>
       <c r="U20" s="4" t="inlineStr">
         <is>
-          <t>无两融数据</t>
+          <t>融资余额下降-1.0%</t>
         </is>
       </c>
       <c r="V20" s="4" t="inlineStr">
@@ -4379,7 +4379,7 @@
       </c>
       <c r="W20" s="4" t="inlineStr">
         <is>
-          <t>近期无重大公告；无两融数据；近期未上龙虎榜</t>
+          <t>近期公告中性；融资余额下降-1.0%；近期未上龙虎榜</t>
         </is>
       </c>
       <c r="X20" s="4" t="n">
@@ -4487,7 +4487,7 @@
         <v>8</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>82.56999999999999</v>
+        <v>83.37</v>
       </c>
       <c r="H21" s="4" t="n">
         <v>5.4</v>
@@ -4523,16 +4523,16 @@
         <v>8.5</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="T21" s="4" t="inlineStr">
         <is>
-          <t>近期无重大公告</t>
+          <t>公告偏风险(1个负面关键词, 0个异动/风险词)</t>
         </is>
       </c>
       <c r="U21" s="4" t="inlineStr">
         <is>
-          <t>无两融数据</t>
+          <t>融资余额上升13.1%</t>
         </is>
       </c>
       <c r="V21" s="4" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="W21" s="4" t="inlineStr">
         <is>
-          <t>近期无重大公告；无两融数据；近期未上龙虎榜</t>
+          <t>公告偏风险(1个负面关键词, 0个异动/风险词)；融资余额上升13.1%；近期未上龙虎榜</t>
         </is>
       </c>
       <c r="X21" s="4" t="n">
